--- a/Översikt KRISTINEHAMN.xlsx
+++ b/Översikt KRISTINEHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45229</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45229</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45727</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>45118</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45265</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>44488</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>45091</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>45561</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>45562</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>45113</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>45233</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>44525</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>44769</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>44574</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>44525</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>44614</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>45002</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>45637</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>45693</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>44584</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>45356</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>44883</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>46141</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>45380</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>45960</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>45960</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>45982</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>46000</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>45154</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>44843</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>45996</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>46101</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>46101</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>45674</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>45804</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>45819</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>44337</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>45579</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>44690</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>44693</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>45247</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>45716</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>45812</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>44831</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>44659</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>44683</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>44466</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>44634</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>44734</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>44851</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>44559</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>44497</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>44536</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>44741</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>44466</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>44576</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>44791</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>44588</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>44588</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>44769</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6495,7 +6495,7 @@
         <v>44829</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>44834</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         <v>44657</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>44497</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>44518</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>44551</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>44501</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>44657</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>44707</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>44662</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>44742</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>44810</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>44880</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>44853</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>44573</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7595,7 +7595,7 @@
         <v>44855</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>44706</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>44591</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>44518</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         <v>44518</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>44501</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8033,7 +8033,7 @@
         <v>44741</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>44584</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>44825</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>44707</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>44706</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8398,7 +8398,7 @@
         <v>45631</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         <v>45442</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>45324</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>45141</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>45081</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>44525</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>44991</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>45095</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>44974</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>45734</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>45272</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>44894</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>45238</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>44841</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         <v>45202</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>45222</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         <v>45456</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9644,7 +9644,7 @@
         <v>45600</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
         <v>44722</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>44959</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>45222</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         <v>45447</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>45662</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>45110</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         <v>45268</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>44588</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>45701</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
         <v>45244</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         <v>44812</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         <v>44917</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>45303</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>44741</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>45253</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>44917</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>45246</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>45202</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>44742</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>44742</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11192,7 +11192,7 @@
         <v>45202</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>45370</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>45044</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>45000</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11484,7 +11484,7 @@
         <v>45041</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>45429</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11630,7 +11630,7 @@
         <v>45678</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>45243</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>45456</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>45666</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>45243</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>45191</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>45167</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>44588</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>45167</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>44734</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>45313</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>45647</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>44473</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>45202</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>45999</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>44917</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>45387</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>45770</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12959,7 +12959,7 @@
         <v>44497</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
         <v>45933</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>45756</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>45252</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>45208</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         <v>45477</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>44474</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>44656</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>45203</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13621,7 +13621,7 @@
         <v>45887</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>45076</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>45079</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>45681</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>45366</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>44648</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>45902</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>46139</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>45904</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14288,7 +14288,7 @@
         <v>45905</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
         <v>45698</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
         <v>45904</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         <v>45681</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>46140</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>45265</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>45379</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>46141</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>46141</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14970,7 +14970,7 @@
         <v>44978</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>46141</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15121,7 +15121,7 @@
         <v>46140</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>44473</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15272,7 +15272,7 @@
         <v>45127</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>45361</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15418,7 +15418,7 @@
         <v>45827</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>45888</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15564,7 +15564,7 @@
         <v>45803</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>45098</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         <v>45392</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>45679</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>46142</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
         <v>45450</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>44526</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>44526</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16163,7 +16163,7 @@
         <v>44712</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>45639</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>45068</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         <v>45631</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>45933</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>44753</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>45477</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>44923</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>44972</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>45268</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>45944</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>45359</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>44466</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>46149</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>45952</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>46150</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17336,7 +17336,7 @@
         <v>45625</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>45954</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>45167</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
         <v>45959</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17638,7 +17638,7 @@
         <v>45959</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>46150</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>45961</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45961</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>44489</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>45453</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>46154</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>45666</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>45341</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>45974</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18388,7 +18388,7 @@
         <v>45569</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>45022</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>45322</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>45268</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>45341</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>45461</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>45313</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>44595</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>44595</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19055,7 +19055,7 @@
         <v>45302</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>44855</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>46161</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>45636</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>45478</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19425,7 +19425,7 @@
         <v>45478</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>45315</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>45622</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>45995</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45995</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>44746</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>45600</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19936,7 +19936,7 @@
         <v>45999</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>46162</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20092,7 +20092,7 @@
         <v>45999</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>45999</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>45999</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>46001</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>46000</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20477,7 +20477,7 @@
         <v>46000</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20555,7 +20555,7 @@
         <v>44941</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20628,7 +20628,7 @@
         <v>46003</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>46003</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20774,7 +20774,7 @@
         <v>46006</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20847,7 +20847,7 @@
         <v>45121</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>46009</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20993,7 +20993,7 @@
         <v>45198</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>46009</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21139,7 +21139,7 @@
         <v>45625</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21212,7 +21212,7 @@
         <v>45450</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>45593</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21363,7 +21363,7 @@
         <v>46170</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>45749</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>45110</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>44831</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>45460</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>45401</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>46034</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>46034</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21947,7 +21947,7 @@
         <v>46171</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22025,7 +22025,7 @@
         <v>46036</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22098,7 +22098,7 @@
         <v>44918</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22176,7 +22176,7 @@
         <v>45176</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22254,7 +22254,7 @@
         <v>46038</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22327,7 +22327,7 @@
         <v>46038</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22400,7 +22400,7 @@
         <v>46038</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>45243</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>45243</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22619,7 +22619,7 @@
         <v>45243</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22692,7 +22692,7 @@
         <v>45686</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22765,7 +22765,7 @@
         <v>45302</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22838,7 +22838,7 @@
         <v>44722</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22911,7 +22911,7 @@
         <v>44722</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>45002</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23057,7 +23057,7 @@
         <v>46049</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>44677</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23203,7 +23203,7 @@
         <v>46048</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23276,7 +23276,7 @@
         <v>45202</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23349,7 +23349,7 @@
         <v>46051</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23422,7 +23422,7 @@
         <v>46175</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23495,7 +23495,7 @@
         <v>45097</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>45302</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23641,7 +23641,7 @@
         <v>45393</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23714,7 +23714,7 @@
         <v>45239</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23787,7 +23787,7 @@
         <v>45058</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>45442</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23938,7 +23938,7 @@
         <v>45226</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24011,7 +24011,7 @@
         <v>45226</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>45260</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24157,7 +24157,7 @@
         <v>45679</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24230,7 +24230,7 @@
         <v>46037</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24303,7 +24303,7 @@
         <v>45379</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24376,7 +24376,7 @@
         <v>45379</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24449,7 +24449,7 @@
         <v>46083</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>46092</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24605,7 +24605,7 @@
         <v>46190</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24678,7 +24678,7 @@
         <v>46092</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>46092</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24834,7 +24834,7 @@
         <v>46094</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>46094</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24990,7 +24990,7 @@
         <v>44883</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>46094</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25141,7 +25141,7 @@
         <v>46190</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25214,7 +25214,7 @@
         <v>45188</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>45072</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25365,7 +25365,7 @@
         <v>44985</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25438,7 +25438,7 @@
         <v>46101</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25516,7 +25516,7 @@
         <v>46101</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         <v>46104</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25667,7 +25667,7 @@
         <v>46106</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25745,7 +25745,7 @@
         <v>46107</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>45202</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>44851</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25969,7 +25969,7 @@
         <v>45181</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26047,7 +26047,7 @@
         <v>45082</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26120,7 +26120,7 @@
         <v>44637</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>45513</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>45141</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26339,7 +26339,7 @@
         <v>45386</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26412,7 +26412,7 @@
         <v>44749</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26485,7 +26485,7 @@
         <v>45112</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26563,7 +26563,7 @@
         <v>46129</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>46129</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>44985</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>45202</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>45112</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26943,7 +26943,7 @@
         <v>44987</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27016,7 +27016,7 @@
         <v>46132</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27089,7 +27089,7 @@
         <v>44924</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>45201</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>45098</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27308,7 +27308,7 @@
         <v>45377</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27381,7 +27381,7 @@
         <v>45104</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         <v>45804</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27527,7 +27527,7 @@
         <v>45888</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27600,7 +27600,7 @@
         <v>45366</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27673,7 +27673,7 @@
         <v>45267</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27746,7 +27746,7 @@
         <v>46136</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27819,7 +27819,7 @@
         <v>45266</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27892,7 +27892,7 @@
         <v>45656</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27965,7 +27965,7 @@
         <v>45811</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>44490</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28111,7 +28111,7 @@
         <v>45323</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>44651</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28257,7 +28257,7 @@
         <v>45379</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>46205</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28403,7 +28403,7 @@
         <v>46205</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>45644</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>44722</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>45685</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>45705</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>45119</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>44533</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
         <v>44847</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>46213</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29060,7 +29060,7 @@
         <v>45595</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>45081</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>45701</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29284,7 +29284,7 @@
         <v>44994</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>45243</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29435,7 +29435,7 @@
         <v>44480</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>45315</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29581,7 +29581,7 @@
         <v>45344</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29659,7 +29659,7 @@
         <v>45282</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29732,7 +29732,7 @@
         <v>45243</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29805,7 +29805,7 @@
         <v>45243</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29878,7 +29878,7 @@
         <v>45118</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>45769</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30029,7 +30029,7 @@
         <v>45159</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>44888</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30180,7 +30180,7 @@
         <v>44722</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30253,7 +30253,7 @@
         <v>45379</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>45478</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30399,7 +30399,7 @@
         <v>44770</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>45701</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30550,7 +30550,7 @@
         <v>45783</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30628,7 +30628,7 @@
         <v>46230</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30701,7 +30701,7 @@
         <v>46274</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>46274</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>45636</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30920,7 +30920,7 @@
         <v>46281</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30993,7 +30993,7 @@
         <v>44805</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31066,7 +31066,7 @@
         <v>46281</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>45792</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31222,7 +31222,7 @@
         <v>45792</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31300,7 +31300,7 @@
         <v>45792</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31378,7 +31378,7 @@
         <v>45792</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>45700</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>45686</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>45407</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>45282</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>46282</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31821,7 +31821,7 @@
         <v>45799</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31899,7 +31899,7 @@
         <v>45575</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31972,7 +31972,7 @@
         <v>46282</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32045,7 +32045,7 @@
         <v>46282</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32118,7 +32118,7 @@
         <v>45553</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32191,7 +32191,7 @@
         <v>45798</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32264,7 +32264,7 @@
         <v>45802</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>45805</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>45805</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>45810</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32571,7 +32571,7 @@
         <v>45810</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32644,7 +32644,7 @@
         <v>45812</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32722,7 +32722,7 @@
         <v>45812</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32800,7 +32800,7 @@
         <v>45820</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>45364</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>45385</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33019,7 +33019,7 @@
         <v>45827</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33092,7 +33092,7 @@
         <v>45378</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33165,7 +33165,7 @@
         <v>45364</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33238,7 +33238,7 @@
         <v>45364</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33311,7 +33311,7 @@
         <v>45833</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>45832</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33457,7 +33457,7 @@
         <v>45833</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33530,7 +33530,7 @@
         <v>45833</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>45664</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33676,7 +33676,7 @@
         <v>45782</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>44965</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33822,7 +33822,7 @@
         <v>45876</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33900,7 +33900,7 @@
         <v>45876</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>43980</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34049,7 +34049,7 @@
         <v>45247</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>45247</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34205,7 +34205,7 @@
         <v>44657</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34278,7 +34278,7 @@
         <v>45103</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34351,7 +34351,7 @@
         <v>44711</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34424,7 +34424,7 @@
         <v>45442</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>45463</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34575,7 +34575,7 @@
         <v>45475</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34648,7 +34648,7 @@
         <v>45533</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34721,7 +34721,7 @@
         <v>44690</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>45442</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34867,7 +34867,7 @@
         <v>44985</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>45414</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>45442</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35086,7 +35086,7 @@
         <v>45533</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>45118</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35232,7 +35232,7 @@
         <v>45247</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35310,7 +35310,7 @@
         <v>45512</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35383,7 +35383,7 @@
         <v>45783</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>45792</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35539,7 +35539,7 @@
         <v>45805</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35617,7 +35617,7 @@
         <v>46040</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35690,7 +35690,7 @@
         <v>46106</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35768,7 +35768,7 @@
         <v>46036</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>

--- a/Översikt KRISTINEHAMN.xlsx
+++ b/Översikt KRISTINEHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45229</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45229</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45727</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>45118</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45265</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>44488</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>45091</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>45561</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>45562</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>45113</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>44690</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>45233</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>44525</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>44769</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>44574</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44525</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>44614</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>45674</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>44584</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>45804</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>45996</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>45637</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>46101</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>46101</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>45960</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>45960</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>45982</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>46000</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>45819</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>44843</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>46141</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>44883</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>45002</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>45380</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>45356</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>45154</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>45693</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>44337</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>44693</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>45579</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>45247</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>45716</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>45812</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>44831</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>44683</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>44659</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>44466</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>44634</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>44734</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>44559</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>44851</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>44497</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>44536</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>44741</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>44466</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>44791</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44576</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>44588</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>44588</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>44769</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>44829</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>44834</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>44657</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>44497</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>44518</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>44551</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>44501</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>44657</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>44707</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>44662</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         <v>44742</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>44810</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>44880</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>44853</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>44573</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>44855</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>44706</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v>44591</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>44518</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>44518</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         <v>44501</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>44741</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         <v>44584</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>44825</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>44707</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>44706</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>45625</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>44742</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>45208</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>45202</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>45377</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
         <v>45202</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         <v>44770</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>45265</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8992,7 +8992,7 @@
         <v>45095</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>45429</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>45282</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
         <v>45447</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>44474</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         <v>44855</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>45393</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
         <v>44888</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>44883</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>45268</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>45686</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>45282</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9868,7 +9868,7 @@
         <v>45407</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         <v>44941</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>45700</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>45243</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         <v>45246</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>45513</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>45553</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         <v>45575</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>45798</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         <v>46034</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         <v>46034</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>45799</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>45477</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>46036</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10895,7 +10895,7 @@
         <v>46038</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>46038</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>46038</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>44656</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>44917</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>44918</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>46048</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>45593</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11484,7 +11484,7 @@
         <v>45902</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>46049</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>45904</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>45905</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>45366</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>46051</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>45121</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>45644</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>44490</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>44917</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>45802</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>45359</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>44677</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>44974</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12516,7 +12516,7 @@
         <v>45803</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>45370</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>45379</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>46083</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>45805</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>45805</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         <v>45810</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>45810</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>45933</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>45625</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>44722</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13339,7 +13339,7 @@
         <v>46092</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>46092</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13495,7 +13495,7 @@
         <v>46092</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>44637</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>45453</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>46094</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13797,7 +13797,7 @@
         <v>46094</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>46094</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>45944</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>46101</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>46101</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>46104</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         <v>46106</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>45812</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14411,7 +14411,7 @@
         <v>45952</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14484,7 +14484,7 @@
         <v>46107</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14557,7 +14557,7 @@
         <v>45954</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>45239</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>44722</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14781,7 +14781,7 @@
         <v>44722</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>45041</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>44466</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>45267</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15073,7 +15073,7 @@
         <v>45959</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15151,7 +15151,7 @@
         <v>45959</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>45961</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>44753</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15380,7 +15380,7 @@
         <v>45961</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>45361</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>45600</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>45812</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>45118</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>45974</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>45058</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>45112</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>44712</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>46129</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>46129</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>45112</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16291,7 +16291,7 @@
         <v>45662</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44924</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>46132</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>45119</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>45141</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>45749</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>45202</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>45701</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>45666</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>45995</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>45887</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>45995</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>46000</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>45999</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>45904</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>46000</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>45999</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>45999</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>45999</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>45888</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>45656</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         <v>46001</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17932,7 +17932,7 @@
         <v>45811</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>45442</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         <v>46003</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>45888</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         <v>44987</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>46140</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         <v>46139</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>45647</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>46003</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>44473</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>45933</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18740,7 +18740,7 @@
         <v>45820</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18813,7 +18813,7 @@
         <v>45002</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>46006</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>45176</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>46009</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19110,7 +19110,7 @@
         <v>45686</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19183,7 +19183,7 @@
         <v>46009</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19256,7 +19256,7 @@
         <v>45804</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19329,7 +19329,7 @@
         <v>44894</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19402,7 +19402,7 @@
         <v>46136</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>46140</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19553,7 +19553,7 @@
         <v>45756</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19631,7 +19631,7 @@
         <v>45999</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19709,7 +19709,7 @@
         <v>45364</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>45364</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>45378</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19928,7 +19928,7 @@
         <v>45127</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20001,7 +20001,7 @@
         <v>45385</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>44533</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>46141</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20225,7 +20225,7 @@
         <v>45364</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20298,7 +20298,7 @@
         <v>46141</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>44917</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>45260</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20522,7 +20522,7 @@
         <v>45827</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>46142</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>45253</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>45827</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20819,7 +20819,7 @@
         <v>46141</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         <v>44847</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>45226</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>45226</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21116,7 +21116,7 @@
         <v>44473</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>45076</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21262,7 +21262,7 @@
         <v>44525</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21335,7 +21335,7 @@
         <v>45366</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>46150</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21486,7 +21486,7 @@
         <v>46149</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21559,7 +21559,7 @@
         <v>46150</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>44923</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21710,7 +21710,7 @@
         <v>45833</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21783,7 +21783,7 @@
         <v>45272</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>45833</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21929,7 +21929,7 @@
         <v>45832</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>45167</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22075,7 +22075,7 @@
         <v>46154</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22148,7 +22148,7 @@
         <v>45833</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>45081</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22294,7 +22294,7 @@
         <v>45664</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>45022</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22440,7 +22440,7 @@
         <v>45341</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22513,7 +22513,7 @@
         <v>45341</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22586,7 +22586,7 @@
         <v>45569</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22659,7 +22659,7 @@
         <v>46161</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22737,7 +22737,7 @@
         <v>45313</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22810,7 +22810,7 @@
         <v>45679</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22883,7 +22883,7 @@
         <v>44994</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22961,7 +22961,7 @@
         <v>45110</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23034,7 +23034,7 @@
         <v>46162</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23112,7 +23112,7 @@
         <v>45081</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>45252</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23258,7 +23258,7 @@
         <v>45238</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23336,7 +23336,7 @@
         <v>45379</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23409,7 +23409,7 @@
         <v>45379</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23482,7 +23482,7 @@
         <v>44985</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23555,7 +23555,7 @@
         <v>45782</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23628,7 +23628,7 @@
         <v>45387</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23706,7 +23706,7 @@
         <v>46170</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
         <v>46171</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23857,7 +23857,7 @@
         <v>45324</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23930,7 +23930,7 @@
         <v>46175</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>44959</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24076,7 +24076,7 @@
         <v>44851</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>45392</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>45000</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
         <v>45110</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>45461</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24446,7 +24446,7 @@
         <v>45698</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24519,7 +24519,7 @@
         <v>45456</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24592,7 +24592,7 @@
         <v>46037</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>45079</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24738,7 +24738,7 @@
         <v>45188</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>45442</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24884,7 +24884,7 @@
         <v>45595</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24957,7 +24957,7 @@
         <v>44965</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>45622</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25103,7 +25103,7 @@
         <v>44588</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>46190</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25254,7 +25254,7 @@
         <v>44588</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25327,7 +25327,7 @@
         <v>45600</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>46190</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>45876</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25551,7 +25551,7 @@
         <v>45876</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25629,7 +25629,7 @@
         <v>45082</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25702,7 +25702,7 @@
         <v>45268</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25775,7 +25775,7 @@
         <v>45478</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>45450</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25926,7 +25926,7 @@
         <v>44648</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>45198</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>44497</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26145,7 +26145,7 @@
         <v>46205</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26218,7 +26218,7 @@
         <v>46205</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>45044</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26364,7 +26364,7 @@
         <v>45313</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>46213</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26510,7 +26510,7 @@
         <v>45456</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26583,7 +26583,7 @@
         <v>44812</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26656,7 +26656,7 @@
         <v>44734</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>44722</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26802,7 +26802,7 @@
         <v>44722</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26875,7 +26875,7 @@
         <v>45666</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26948,7 +26948,7 @@
         <v>45181</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>45202</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>45769</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27177,7 +27177,7 @@
         <v>45243</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27250,7 +27250,7 @@
         <v>44749</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27323,7 +27323,7 @@
         <v>45701</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27401,7 +27401,7 @@
         <v>45631</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27474,7 +27474,7 @@
         <v>45191</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27547,7 +27547,7 @@
         <v>45201</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>45302</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>45159</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27771,7 +27771,7 @@
         <v>45315</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27844,7 +27844,7 @@
         <v>45770</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27917,7 +27917,7 @@
         <v>45344</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27995,7 +27995,7 @@
         <v>44831</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>45097</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>45202</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>44480</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>45303</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         <v>45379</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28433,7 +28433,7 @@
         <v>46274</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
         <v>46274</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>46230</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>45244</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
         <v>45681</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28803,7 +28803,7 @@
         <v>45678</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28876,7 +28876,7 @@
         <v>46282</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28949,7 +28949,7 @@
         <v>45386</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29022,7 +29022,7 @@
         <v>45302</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
         <v>46281</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29168,7 +29168,7 @@
         <v>46281</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29246,7 +29246,7 @@
         <v>46282</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29319,7 +29319,7 @@
         <v>45681</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29397,7 +29397,7 @@
         <v>46282</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29470,7 +29470,7 @@
         <v>46286</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29548,7 +29548,7 @@
         <v>45477</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29621,7 +29621,7 @@
         <v>45268</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>44651</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29767,7 +29767,7 @@
         <v>44841</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29840,7 +29840,7 @@
         <v>44741</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>45302</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29991,7 +29991,7 @@
         <v>45203</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30064,7 +30064,7 @@
         <v>45460</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30137,7 +30137,7 @@
         <v>45222</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>44489</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>45478</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>45478</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30429,7 +30429,7 @@
         <v>45098</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30502,7 +30502,7 @@
         <v>45098</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30575,7 +30575,7 @@
         <v>45701</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30653,7 +30653,7 @@
         <v>44526</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30726,7 +30726,7 @@
         <v>44526</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30799,7 +30799,7 @@
         <v>45104</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30872,7 +30872,7 @@
         <v>44595</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>44595</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>45243</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31101,7 +31101,7 @@
         <v>45243</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31174,7 +31174,7 @@
         <v>45243</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31247,7 +31247,7 @@
         <v>45322</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31320,7 +31320,7 @@
         <v>45266</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31393,7 +31393,7 @@
         <v>44978</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31466,7 +31466,7 @@
         <v>44746</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31539,7 +31539,7 @@
         <v>45639</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>45450</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31690,7 +31690,7 @@
         <v>45072</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31768,7 +31768,7 @@
         <v>45167</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31841,7 +31841,7 @@
         <v>44972</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31914,7 +31914,7 @@
         <v>45068</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31987,7 +31987,7 @@
         <v>45202</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32060,7 +32060,7 @@
         <v>45401</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32133,7 +32133,7 @@
         <v>45141</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32206,7 +32206,7 @@
         <v>45243</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32279,7 +32279,7 @@
         <v>45243</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32352,7 +32352,7 @@
         <v>45315</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>45243</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>45167</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32571,7 +32571,7 @@
         <v>45323</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32644,7 +32644,7 @@
         <v>44985</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32717,7 +32717,7 @@
         <v>44991</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32790,7 +32790,7 @@
         <v>45631</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32863,7 +32863,7 @@
         <v>44742</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32936,7 +32936,7 @@
         <v>45705</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33009,7 +33009,7 @@
         <v>45734</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33082,7 +33082,7 @@
         <v>45202</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33155,7 +33155,7 @@
         <v>45222</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>45379</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33306,7 +33306,7 @@
         <v>45636</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33379,7 +33379,7 @@
         <v>45679</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>45685</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33525,7 +33525,7 @@
         <v>45783</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>45636</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33676,7 +33676,7 @@
         <v>45792</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33754,7 +33754,7 @@
         <v>45792</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33832,7 +33832,7 @@
         <v>45792</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33910,7 +33910,7 @@
         <v>44805</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33983,7 +33983,7 @@
         <v>45792</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34059,7 +34059,7 @@
         <v>43980</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34132,7 +34132,7 @@
         <v>44657</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34205,7 +34205,7 @@
         <v>44711</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34278,7 +34278,7 @@
         <v>44690</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34351,7 +34351,7 @@
         <v>45247</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34429,7 +34429,7 @@
         <v>45247</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34507,7 +34507,7 @@
         <v>45103</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34580,7 +34580,7 @@
         <v>45442</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>45463</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>45475</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>45533</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34877,7 +34877,7 @@
         <v>45442</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>44985</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>45414</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35096,7 +35096,7 @@
         <v>45442</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35169,7 +35169,7 @@
         <v>45533</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35242,7 +35242,7 @@
         <v>45118</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>45247</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35393,7 +35393,7 @@
         <v>45512</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>45783</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35544,7 +35544,7 @@
         <v>45792</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35622,7 +35622,7 @@
         <v>45805</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35700,7 +35700,7 @@
         <v>46040</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>46106</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35851,7 +35851,7 @@
         <v>46036</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>

--- a/Översikt KRISTINEHAMN.xlsx
+++ b/Översikt KRISTINEHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45229</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45229</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45727</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>45118</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45265</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>44488</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>45091</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>45561</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>45562</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>45113</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>44690</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>45233</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>44525</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>44769</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>44574</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44525</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>44614</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>45674</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>44584</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>45804</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>45996</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>45637</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>46101</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>46101</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>45960</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>45960</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>45982</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>46000</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>45819</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>44843</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>46141</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>44883</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>45002</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>45380</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>45356</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>45154</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>45693</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>44337</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>44693</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>45579</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>45247</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>45716</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>45812</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>44831</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>44683</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>44659</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>44466</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>44634</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>44734</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>44559</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>44851</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>44497</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>44536</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>44741</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>44466</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>44791</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44576</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>44588</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>44588</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>44769</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>44829</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>44834</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>44657</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>44497</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>44518</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>44551</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>44501</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>44657</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>44707</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>44662</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         <v>44742</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>44810</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>44880</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>44853</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>44573</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>44855</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>44706</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v>44591</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>44518</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>44518</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         <v>44501</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>44741</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         <v>44584</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>44825</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>44707</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>44706</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>45625</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>44742</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>45208</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>45202</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>45377</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
         <v>45202</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         <v>44770</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>45265</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8992,7 +8992,7 @@
         <v>45095</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>45429</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>45282</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
         <v>45447</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>44474</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         <v>44855</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>45393</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
         <v>44888</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>44883</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>45268</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>45686</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>45282</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9868,7 +9868,7 @@
         <v>45407</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         <v>44941</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>45700</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>45243</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         <v>45246</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>45513</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>45553</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         <v>45575</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>45798</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         <v>46034</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         <v>46034</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>45799</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>45477</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>46036</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10895,7 +10895,7 @@
         <v>46038</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>46038</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>46038</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>44656</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>44917</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>44918</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>46048</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>45593</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11484,7 +11484,7 @@
         <v>45902</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>46049</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>45904</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>45905</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>45366</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>46051</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>45121</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>45644</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>44490</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>44917</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>45802</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>45359</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>44677</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>44974</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12516,7 +12516,7 @@
         <v>45803</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>45370</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>45379</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>46083</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>45805</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>45805</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         <v>45810</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>45810</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>45933</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>45625</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>44722</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13339,7 +13339,7 @@
         <v>46092</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>46092</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13495,7 +13495,7 @@
         <v>46092</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>44637</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>45453</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>46094</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13797,7 +13797,7 @@
         <v>46094</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>46094</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>45944</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>46101</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>46101</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>46104</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         <v>46106</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>45812</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14411,7 +14411,7 @@
         <v>45952</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14484,7 +14484,7 @@
         <v>46107</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14557,7 +14557,7 @@
         <v>45954</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>45239</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>44722</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14781,7 +14781,7 @@
         <v>44722</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>45041</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>44466</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>45267</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15073,7 +15073,7 @@
         <v>45959</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15151,7 +15151,7 @@
         <v>45959</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>45961</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>44753</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15380,7 +15380,7 @@
         <v>45961</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>45361</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>45600</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>45812</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>45118</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>45974</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>45058</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>45112</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>44712</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>46129</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>46129</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>45112</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16291,7 +16291,7 @@
         <v>45662</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44924</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>46132</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>45119</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>45141</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>45749</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>45202</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>45701</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>45666</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>45995</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>45887</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>45995</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>46000</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>45999</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>45904</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>46000</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>45999</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>45999</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>45999</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>45888</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>45656</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         <v>46001</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17932,7 +17932,7 @@
         <v>45811</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>45442</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         <v>46003</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>45888</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         <v>44987</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>46140</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         <v>46139</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>45647</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>46003</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>44473</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>45933</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18740,7 +18740,7 @@
         <v>45820</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18813,7 +18813,7 @@
         <v>45002</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>46006</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>45176</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>46009</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19110,7 +19110,7 @@
         <v>45686</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19183,7 +19183,7 @@
         <v>46009</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19256,7 +19256,7 @@
         <v>45804</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19329,7 +19329,7 @@
         <v>44894</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19402,7 +19402,7 @@
         <v>46136</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>46140</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19553,7 +19553,7 @@
         <v>45756</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19631,7 +19631,7 @@
         <v>45999</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19709,7 +19709,7 @@
         <v>45364</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>45364</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>45378</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19928,7 +19928,7 @@
         <v>45127</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20001,7 +20001,7 @@
         <v>45385</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>44533</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>46141</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20225,7 +20225,7 @@
         <v>45364</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20298,7 +20298,7 @@
         <v>46141</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>44917</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>45260</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20522,7 +20522,7 @@
         <v>45827</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>46142</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>45253</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>45827</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20819,7 +20819,7 @@
         <v>46141</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         <v>44847</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>45226</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>45226</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21116,7 +21116,7 @@
         <v>44473</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>45076</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21262,7 +21262,7 @@
         <v>44525</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21335,7 +21335,7 @@
         <v>45366</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>46150</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21486,7 +21486,7 @@
         <v>46149</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21559,7 +21559,7 @@
         <v>46150</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>44923</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21710,7 +21710,7 @@
         <v>45833</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21783,7 +21783,7 @@
         <v>45272</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>45833</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21929,7 +21929,7 @@
         <v>45832</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>45167</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22075,7 +22075,7 @@
         <v>46154</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22148,7 +22148,7 @@
         <v>45833</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>45081</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22294,7 +22294,7 @@
         <v>45664</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>45022</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22440,7 +22440,7 @@
         <v>45341</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22513,7 +22513,7 @@
         <v>45341</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22586,7 +22586,7 @@
         <v>45569</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22659,7 +22659,7 @@
         <v>46161</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22737,7 +22737,7 @@
         <v>45313</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22810,7 +22810,7 @@
         <v>45679</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22883,7 +22883,7 @@
         <v>44994</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22961,7 +22961,7 @@
         <v>45110</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23034,7 +23034,7 @@
         <v>46162</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23112,7 +23112,7 @@
         <v>45081</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>45252</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23258,7 +23258,7 @@
         <v>45238</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23336,7 +23336,7 @@
         <v>45379</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23409,7 +23409,7 @@
         <v>45379</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23482,7 +23482,7 @@
         <v>44985</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23555,7 +23555,7 @@
         <v>45782</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23628,7 +23628,7 @@
         <v>45387</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23706,7 +23706,7 @@
         <v>46170</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
         <v>46171</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23857,7 +23857,7 @@
         <v>45324</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23930,7 +23930,7 @@
         <v>46175</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>44959</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24076,7 +24076,7 @@
         <v>44851</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>45392</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>45000</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
         <v>45110</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>45461</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24446,7 +24446,7 @@
         <v>45698</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24519,7 +24519,7 @@
         <v>45456</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24592,7 +24592,7 @@
         <v>46037</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>45079</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24738,7 +24738,7 @@
         <v>45188</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>45442</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24884,7 +24884,7 @@
         <v>45595</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24957,7 +24957,7 @@
         <v>44965</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>45622</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25103,7 +25103,7 @@
         <v>44588</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>46190</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25254,7 +25254,7 @@
         <v>44588</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25327,7 +25327,7 @@
         <v>45600</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>46190</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>45876</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25551,7 +25551,7 @@
         <v>45876</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25629,7 +25629,7 @@
         <v>45082</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25702,7 +25702,7 @@
         <v>45268</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25775,7 +25775,7 @@
         <v>45478</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>45450</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25926,7 +25926,7 @@
         <v>44648</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>45198</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>44497</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26145,7 +26145,7 @@
         <v>46205</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26218,7 +26218,7 @@
         <v>46205</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>45044</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26364,7 +26364,7 @@
         <v>45313</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>46213</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26510,7 +26510,7 @@
         <v>45456</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26583,7 +26583,7 @@
         <v>44812</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26656,7 +26656,7 @@
         <v>44734</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>44722</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26802,7 +26802,7 @@
         <v>44722</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26875,7 +26875,7 @@
         <v>45666</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26948,7 +26948,7 @@
         <v>45181</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>45202</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>45769</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27177,7 +27177,7 @@
         <v>45243</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27250,7 +27250,7 @@
         <v>44749</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27323,7 +27323,7 @@
         <v>45701</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27401,7 +27401,7 @@
         <v>45631</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27474,7 +27474,7 @@
         <v>45191</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27547,7 +27547,7 @@
         <v>45201</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>45302</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>45159</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27771,7 +27771,7 @@
         <v>45315</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27844,7 +27844,7 @@
         <v>45770</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27917,7 +27917,7 @@
         <v>45344</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27995,7 +27995,7 @@
         <v>44831</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>45097</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>45202</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>44480</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>45303</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         <v>45379</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28433,7 +28433,7 @@
         <v>46274</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
         <v>46274</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>46230</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>45244</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
         <v>45681</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28803,7 +28803,7 @@
         <v>45678</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28876,7 +28876,7 @@
         <v>46282</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28949,7 +28949,7 @@
         <v>45386</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29022,7 +29022,7 @@
         <v>45302</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
         <v>46281</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29168,7 +29168,7 @@
         <v>46281</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29246,7 +29246,7 @@
         <v>46282</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29319,7 +29319,7 @@
         <v>45681</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29397,7 +29397,7 @@
         <v>46282</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29470,7 +29470,7 @@
         <v>46286</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29548,7 +29548,7 @@
         <v>45477</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29621,7 +29621,7 @@
         <v>45268</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>44651</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29767,7 +29767,7 @@
         <v>44841</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29840,7 +29840,7 @@
         <v>44741</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>45302</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29991,7 +29991,7 @@
         <v>45203</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30064,7 +30064,7 @@
         <v>45460</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30137,7 +30137,7 @@
         <v>45222</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>44489</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>45478</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>45478</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30429,7 +30429,7 @@
         <v>45098</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30502,7 +30502,7 @@
         <v>45098</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30575,7 +30575,7 @@
         <v>45701</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30653,7 +30653,7 @@
         <v>44526</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30726,7 +30726,7 @@
         <v>44526</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30799,7 +30799,7 @@
         <v>45104</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30872,7 +30872,7 @@
         <v>44595</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>44595</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>45243</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31101,7 +31101,7 @@
         <v>45243</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31174,7 +31174,7 @@
         <v>45243</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31247,7 +31247,7 @@
         <v>45322</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31320,7 +31320,7 @@
         <v>45266</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31393,7 +31393,7 @@
         <v>44978</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31466,7 +31466,7 @@
         <v>44746</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31539,7 +31539,7 @@
         <v>45639</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>45450</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31690,7 +31690,7 @@
         <v>45072</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31768,7 +31768,7 @@
         <v>45167</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31841,7 +31841,7 @@
         <v>44972</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31914,7 +31914,7 @@
         <v>45068</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31987,7 +31987,7 @@
         <v>45202</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32060,7 +32060,7 @@
         <v>45401</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32133,7 +32133,7 @@
         <v>45141</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32206,7 +32206,7 @@
         <v>45243</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32279,7 +32279,7 @@
         <v>45243</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32352,7 +32352,7 @@
         <v>45315</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>45243</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>45167</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32571,7 +32571,7 @@
         <v>45323</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32644,7 +32644,7 @@
         <v>44985</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32717,7 +32717,7 @@
         <v>44991</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32790,7 +32790,7 @@
         <v>45631</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32863,7 +32863,7 @@
         <v>44742</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32936,7 +32936,7 @@
         <v>45705</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33009,7 +33009,7 @@
         <v>45734</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33082,7 +33082,7 @@
         <v>45202</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33155,7 +33155,7 @@
         <v>45222</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>45379</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33306,7 +33306,7 @@
         <v>45636</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33379,7 +33379,7 @@
         <v>45679</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>45685</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33525,7 +33525,7 @@
         <v>45783</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>45636</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33676,7 +33676,7 @@
         <v>45792</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33754,7 +33754,7 @@
         <v>45792</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33832,7 +33832,7 @@
         <v>45792</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33910,7 +33910,7 @@
         <v>44805</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33983,7 +33983,7 @@
         <v>45792</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34059,7 +34059,7 @@
         <v>43980</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34132,7 +34132,7 @@
         <v>44657</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34205,7 +34205,7 @@
         <v>44711</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34278,7 +34278,7 @@
         <v>44690</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34351,7 +34351,7 @@
         <v>45247</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34429,7 +34429,7 @@
         <v>45247</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34507,7 +34507,7 @@
         <v>45103</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34580,7 +34580,7 @@
         <v>45442</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>45463</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>45475</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>45533</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34877,7 +34877,7 @@
         <v>45442</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>44985</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>45414</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35096,7 +35096,7 @@
         <v>45442</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35169,7 +35169,7 @@
         <v>45533</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35242,7 +35242,7 @@
         <v>45118</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>45247</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35393,7 +35393,7 @@
         <v>45512</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>45783</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35544,7 +35544,7 @@
         <v>45792</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35622,7 +35622,7 @@
         <v>45805</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35700,7 +35700,7 @@
         <v>46040</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>46106</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35851,7 +35851,7 @@
         <v>46036</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>

--- a/Översikt KRISTINEHAMN.xlsx
+++ b/Översikt KRISTINEHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45229</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45229</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45727</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>45118</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45265</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>44488</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>45091</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>45561</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>45562</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>45113</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>45233</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>44690</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>44525</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>44769</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>44574</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44525</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>44614</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>45002</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>45637</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>45693</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>45674</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>45804</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>44584</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>45996</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>45960</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>45960</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>46101</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>46101</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>45356</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>45819</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>45982</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>46000</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>44883</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>46141</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>45380</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>45154</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>44843</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>44337</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>45579</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>44693</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>45247</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>45716</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>45812</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>44831</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>44683</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>44634</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>44659</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>44734</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>44851</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>44559</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>44497</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>44536</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>44741</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>44791</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>44576</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>44588</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44588</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>44769</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>44829</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>44834</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>44657</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>44497</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>44518</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>44551</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>44501</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>44657</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>44707</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>44662</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>44742</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>44810</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         <v>44880</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>44853</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>44573</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>44855</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>44706</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>44591</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>44518</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v>44518</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>44501</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>44741</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         <v>44584</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>44825</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         <v>44707</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>44706</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>45631</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>45081</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>45324</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>44841</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>45141</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>45442</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>44525</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
         <v>44991</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         <v>45095</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>44974</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>45734</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         <v>45272</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>44894</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>45238</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>44722</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         <v>46000</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>45222</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>45456</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
         <v>45600</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>46003</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>46003</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>44805</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>45202</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>46006</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>46009</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>44497</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>46009</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>44959</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>45222</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>45477</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>45447</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>45662</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>45110</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>46034</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>46034</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>45902</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>46036</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>45905</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>45792</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
         <v>45904</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>46038</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>46038</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>46038</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         <v>45792</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>45792</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>45792</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11655,7 +11655,7 @@
         <v>45700</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11728,7 +11728,7 @@
         <v>45686</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11801,7 +11801,7 @@
         <v>45407</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>44588</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>45701</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>45282</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>46049</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
         <v>46048</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>45799</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>45575</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12395,7 +12395,7 @@
         <v>46051</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>45553</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>45798</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>45044</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>45802</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>45268</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>45805</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12916,7 +12916,7 @@
         <v>45805</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         <v>45244</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>44812</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13140,7 +13140,7 @@
         <v>45303</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13213,7 +13213,7 @@
         <v>45803</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>45810</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>44917</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>44741</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13515,7 +13515,7 @@
         <v>45253</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>45933</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>44917</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>45246</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>45202</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>45944</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>44742</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>44742</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>45202</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>45370</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>45810</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>45000</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>45952</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>46083</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>45812</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>45812</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>45954</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
         <v>45959</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>45959</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14932,7 +14932,7 @@
         <v>46092</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>45041</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>45961</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>45961</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>46092</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>46092</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>46094</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>46094</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>46094</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15629,7 +15629,7 @@
         <v>45429</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>45678</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>45243</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15848,7 +15848,7 @@
         <v>45456</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15921,7 +15921,7 @@
         <v>45974</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         <v>46101</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
         <v>46101</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>46104</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>45666</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16296,7 +16296,7 @@
         <v>46106</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>45167</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>44588</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>45167</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>45243</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16671,7 +16671,7 @@
         <v>45191</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>44734</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>46107</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>45820</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>45313</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         <v>45647</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>44473</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17182,7 +17182,7 @@
         <v>45202</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
         <v>45364</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>44917</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>45385</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
         <v>45995</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>45387</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17625,7 +17625,7 @@
         <v>45827</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17698,7 +17698,7 @@
         <v>45770</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>45995</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17844,7 +17844,7 @@
         <v>45378</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17917,7 +17917,7 @@
         <v>45364</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17990,7 +17990,7 @@
         <v>45999</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         <v>45999</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18146,7 +18146,7 @@
         <v>45364</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18219,7 +18219,7 @@
         <v>45112</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>46129</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         <v>46129</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>45999</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18531,7 +18531,7 @@
         <v>45999</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18609,7 +18609,7 @@
         <v>45112</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18687,7 +18687,7 @@
         <v>46001</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>46000</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18838,7 +18838,7 @@
         <v>46132</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18911,7 +18911,7 @@
         <v>45833</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18984,7 +18984,7 @@
         <v>45832</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         <v>45833</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19130,7 +19130,7 @@
         <v>45833</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         <v>45252</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>45208</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
         <v>45664</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19422,7 +19422,7 @@
         <v>44474</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19495,7 +19495,7 @@
         <v>44656</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>45203</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19641,7 +19641,7 @@
         <v>45804</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19714,7 +19714,7 @@
         <v>45888</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>45076</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>46136</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>45079</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20006,7 +20006,7 @@
         <v>45681</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>45811</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20157,7 +20157,7 @@
         <v>45366</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>44648</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20303,7 +20303,7 @@
         <v>45999</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>45933</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>45681</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20532,7 +20532,7 @@
         <v>45265</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20610,7 +20610,7 @@
         <v>45379</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>45756</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>44978</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>44473</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>45361</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20980,7 +20980,7 @@
         <v>45887</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>45782</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>46139</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21199,7 +21199,7 @@
         <v>45098</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21272,7 +21272,7 @@
         <v>45904</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>45392</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>45679</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>45450</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21569,7 +21569,7 @@
         <v>44526</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21642,7 +21642,7 @@
         <v>44526</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         <v>46140</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>44712</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21866,7 +21866,7 @@
         <v>45639</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>46141</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22017,7 +22017,7 @@
         <v>45068</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>45631</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22163,7 +22163,7 @@
         <v>46141</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
         <v>44753</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22314,7 +22314,7 @@
         <v>45477</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>46141</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>44923</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22538,7 +22538,7 @@
         <v>46140</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>44972</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22689,7 +22689,7 @@
         <v>45127</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>45268</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>45827</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22908,7 +22908,7 @@
         <v>45359</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>45888</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>46142</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23132,7 +23132,7 @@
         <v>44965</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>45625</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>46149</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23351,7 +23351,7 @@
         <v>45167</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>46150</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23502,7 +23502,7 @@
         <v>46150</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>44489</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         <v>46154</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
         <v>45341</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>45569</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23872,7 +23872,7 @@
         <v>45022</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23945,7 +23945,7 @@
         <v>45341</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>45453</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24091,7 +24091,7 @@
         <v>46161</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>45666</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>45322</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24315,7 +24315,7 @@
         <v>45876</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24393,7 +24393,7 @@
         <v>45268</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24466,7 +24466,7 @@
         <v>46162</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24544,7 +24544,7 @@
         <v>45876</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24622,7 +24622,7 @@
         <v>45461</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24695,7 +24695,7 @@
         <v>45313</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>44595</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>44595</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>45302</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>46170</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>44855</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>46171</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>45636</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25294,7 +25294,7 @@
         <v>46175</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25367,7 +25367,7 @@
         <v>45478</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25440,7 +25440,7 @@
         <v>45478</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25513,7 +25513,7 @@
         <v>45315</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25586,7 +25586,7 @@
         <v>45622</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25659,7 +25659,7 @@
         <v>44746</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>45600</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25805,7 +25805,7 @@
         <v>46037</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         <v>44941</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>46190</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>46190</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26097,7 +26097,7 @@
         <v>45121</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>45198</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26243,7 +26243,7 @@
         <v>45625</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26316,7 +26316,7 @@
         <v>45450</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26394,7 +26394,7 @@
         <v>45593</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26467,7 +26467,7 @@
         <v>45749</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26540,7 +26540,7 @@
         <v>45110</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26613,7 +26613,7 @@
         <v>44831</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26686,7 +26686,7 @@
         <v>45460</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26759,7 +26759,7 @@
         <v>45401</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26832,7 +26832,7 @@
         <v>46205</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>46205</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         <v>44918</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27056,7 +27056,7 @@
         <v>45176</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27134,7 +27134,7 @@
         <v>45243</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>45243</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>45243</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27353,7 +27353,7 @@
         <v>45686</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27426,7 +27426,7 @@
         <v>45302</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>44722</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27572,7 +27572,7 @@
         <v>44722</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>45002</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27718,7 +27718,7 @@
         <v>44677</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>45202</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>45097</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27937,7 +27937,7 @@
         <v>45302</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28010,7 +28010,7 @@
         <v>45393</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28083,7 +28083,7 @@
         <v>45239</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28156,7 +28156,7 @@
         <v>45058</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28234,7 +28234,7 @@
         <v>45442</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28307,7 +28307,7 @@
         <v>45226</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>45226</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28453,7 +28453,7 @@
         <v>45260</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>45679</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28599,7 +28599,7 @@
         <v>45379</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>45379</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28745,7 +28745,7 @@
         <v>46230</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28818,7 +28818,7 @@
         <v>46274</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28891,7 +28891,7 @@
         <v>46274</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28964,7 +28964,7 @@
         <v>46281</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29037,7 +29037,7 @@
         <v>46281</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29115,7 +29115,7 @@
         <v>44883</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29188,7 +29188,7 @@
         <v>45188</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         <v>46282</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29334,7 +29334,7 @@
         <v>45072</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>46282</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>46282</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29558,7 +29558,7 @@
         <v>44985</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29631,7 +29631,7 @@
         <v>46286</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29709,7 +29709,7 @@
         <v>45202</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>44851</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29860,7 +29860,7 @@
         <v>45181</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29938,7 +29938,7 @@
         <v>45082</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30011,7 +30011,7 @@
         <v>44637</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30084,7 +30084,7 @@
         <v>45513</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>45141</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30230,7 +30230,7 @@
         <v>45386</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         <v>44749</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30376,7 +30376,7 @@
         <v>44985</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30449,7 +30449,7 @@
         <v>45202</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>44987</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>44924</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>45201</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30741,7 +30741,7 @@
         <v>45098</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>46293</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30887,7 +30887,7 @@
         <v>45377</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30960,7 +30960,7 @@
         <v>45104</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>45366</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31106,7 +31106,7 @@
         <v>45267</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
         <v>45266</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31252,7 +31252,7 @@
         <v>45656</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31325,7 +31325,7 @@
         <v>44490</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31398,7 +31398,7 @@
         <v>45323</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31471,7 +31471,7 @@
         <v>44651</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31544,7 +31544,7 @@
         <v>46287</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31617,7 +31617,7 @@
         <v>45379</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31690,7 +31690,7 @@
         <v>45644</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31763,7 +31763,7 @@
         <v>44722</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>46213</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>45685</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31982,7 +31982,7 @@
         <v>45705</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>45119</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32128,7 +32128,7 @@
         <v>44533</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32201,7 +32201,7 @@
         <v>44847</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>45595</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32347,7 +32347,7 @@
         <v>45081</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>45701</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>44994</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>45243</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>44480</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32722,7 +32722,7 @@
         <v>45315</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32795,7 +32795,7 @@
         <v>45344</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>45282</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>45243</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33019,7 +33019,7 @@
         <v>45243</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33092,7 +33092,7 @@
         <v>45118</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33165,7 +33165,7 @@
         <v>45769</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33243,7 +33243,7 @@
         <v>45159</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33321,7 +33321,7 @@
         <v>44888</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33394,7 +33394,7 @@
         <v>44722</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33467,7 +33467,7 @@
         <v>45379</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>45478</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33613,7 +33613,7 @@
         <v>44770</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33686,7 +33686,7 @@
         <v>45701</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33764,7 +33764,7 @@
         <v>45783</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33842,7 +33842,7 @@
         <v>45636</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>43980</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>45247</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34064,7 +34064,7 @@
         <v>45247</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34142,7 +34142,7 @@
         <v>44657</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>45103</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34288,7 +34288,7 @@
         <v>44711</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34361,7 +34361,7 @@
         <v>45442</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34434,7 +34434,7 @@
         <v>45463</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34512,7 +34512,7 @@
         <v>45475</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34585,7 +34585,7 @@
         <v>45533</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34658,7 +34658,7 @@
         <v>44690</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>45442</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>44985</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34877,7 +34877,7 @@
         <v>45414</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>45442</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>45533</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35096,7 +35096,7 @@
         <v>45118</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35169,7 +35169,7 @@
         <v>45247</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>45512</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35320,7 +35320,7 @@
         <v>45783</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35398,7 +35398,7 @@
         <v>45792</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35476,7 +35476,7 @@
         <v>45805</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35554,7 +35554,7 @@
         <v>46040</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35627,7 +35627,7 @@
         <v>46106</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35705,7 +35705,7 @@
         <v>46036</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>

--- a/Översikt KRISTINEHAMN.xlsx
+++ b/Översikt KRISTINEHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45229</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45229</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45727</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>45118</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45265</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>44488</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>45091</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>45561</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>45562</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>45113</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>45233</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>44690</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>44525</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>44769</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>44574</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44525</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>44614</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>45002</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>45637</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>45693</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>45674</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>45804</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>44584</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>45996</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>45960</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>45960</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>46101</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>46101</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>45356</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>45819</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>45982</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>46000</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>44883</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>46141</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>45380</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>45154</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>44843</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>44337</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>45579</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>44693</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>45247</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>45716</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>45812</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>44831</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>44683</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>44634</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>44659</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>44734</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>44851</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>44559</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>44497</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>44536</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>44741</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>44791</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>44576</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>44588</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44588</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>44769</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>44829</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>44834</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>44657</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>44497</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>44518</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>44551</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>44501</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>44657</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>44707</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>44662</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>44742</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>44810</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         <v>44880</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>44853</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>44573</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>44855</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>44706</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>44591</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>44518</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v>44518</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>44501</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>44741</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         <v>44584</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>44825</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         <v>44707</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>44706</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>45631</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>45081</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>45324</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>44841</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>45141</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>45442</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>44525</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
         <v>44991</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         <v>45095</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>44974</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>45734</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         <v>45272</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>44894</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>45238</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>44722</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         <v>46000</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>45222</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>45456</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
         <v>45600</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>46003</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>46003</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>44805</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>45202</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>46006</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>46009</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>44497</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>46009</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>44959</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>45222</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>45477</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>45447</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>45662</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>45110</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>46034</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>46034</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>45902</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>46036</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>45905</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>45792</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
         <v>45904</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>46038</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>46038</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>46038</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         <v>45792</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>45792</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>45792</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11655,7 +11655,7 @@
         <v>45700</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11728,7 +11728,7 @@
         <v>45686</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11801,7 +11801,7 @@
         <v>45407</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>44588</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>45701</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>45282</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>46049</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
         <v>46048</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>45799</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>45575</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12395,7 +12395,7 @@
         <v>46051</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>45553</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>45798</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>45044</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>45802</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>45268</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>45805</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12916,7 +12916,7 @@
         <v>45805</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         <v>45244</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>44812</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13140,7 +13140,7 @@
         <v>45303</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13213,7 +13213,7 @@
         <v>45803</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>45810</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>44917</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>44741</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13515,7 +13515,7 @@
         <v>45253</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>45933</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>44917</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>45246</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>45202</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>45944</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>44742</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>44742</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>45202</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>45370</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>45810</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>45000</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>45952</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>46083</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>45812</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>45812</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>45954</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
         <v>45959</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>45959</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14932,7 +14932,7 @@
         <v>46092</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>45041</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>45961</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>45961</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>46092</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>46092</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>46094</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>46094</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>46094</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15629,7 +15629,7 @@
         <v>45429</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>45678</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>45243</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15848,7 +15848,7 @@
         <v>45456</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15921,7 +15921,7 @@
         <v>45974</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         <v>46101</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
         <v>46101</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>46104</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>45666</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16296,7 +16296,7 @@
         <v>46106</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>45167</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>44588</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>45167</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>45243</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16671,7 +16671,7 @@
         <v>45191</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>44734</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>46107</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>45820</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>45313</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         <v>45647</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>44473</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17182,7 +17182,7 @@
         <v>45202</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
         <v>45364</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>44917</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>45385</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
         <v>45995</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>45387</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17625,7 +17625,7 @@
         <v>45827</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17698,7 +17698,7 @@
         <v>45770</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>45995</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17844,7 +17844,7 @@
         <v>45378</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17917,7 +17917,7 @@
         <v>45364</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17990,7 +17990,7 @@
         <v>45999</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         <v>45999</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18146,7 +18146,7 @@
         <v>45364</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18219,7 +18219,7 @@
         <v>45112</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>46129</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         <v>46129</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>45999</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18531,7 +18531,7 @@
         <v>45999</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18609,7 +18609,7 @@
         <v>45112</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18687,7 +18687,7 @@
         <v>46001</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>46000</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18838,7 +18838,7 @@
         <v>46132</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18911,7 +18911,7 @@
         <v>45833</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18984,7 +18984,7 @@
         <v>45832</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         <v>45833</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19130,7 +19130,7 @@
         <v>45833</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         <v>45252</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>45208</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
         <v>45664</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19422,7 +19422,7 @@
         <v>44474</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19495,7 +19495,7 @@
         <v>44656</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>45203</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19641,7 +19641,7 @@
         <v>45804</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19714,7 +19714,7 @@
         <v>45888</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>45076</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>46136</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>45079</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20006,7 +20006,7 @@
         <v>45681</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>45811</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20157,7 +20157,7 @@
         <v>45366</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>44648</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20303,7 +20303,7 @@
         <v>45999</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>45933</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>45681</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20532,7 +20532,7 @@
         <v>45265</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20610,7 +20610,7 @@
         <v>45379</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>45756</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>44978</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>44473</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>45361</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20980,7 +20980,7 @@
         <v>45887</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>45782</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>46139</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21199,7 +21199,7 @@
         <v>45098</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21272,7 +21272,7 @@
         <v>45904</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>45392</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>45679</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>45450</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21569,7 +21569,7 @@
         <v>44526</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21642,7 +21642,7 @@
         <v>44526</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         <v>46140</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>44712</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21866,7 +21866,7 @@
         <v>45639</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>46141</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22017,7 +22017,7 @@
         <v>45068</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>45631</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22163,7 +22163,7 @@
         <v>46141</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
         <v>44753</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22314,7 +22314,7 @@
         <v>45477</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>46141</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>44923</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22538,7 +22538,7 @@
         <v>46140</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>44972</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22689,7 +22689,7 @@
         <v>45127</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>45268</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>45827</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22908,7 +22908,7 @@
         <v>45359</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>45888</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>46142</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23132,7 +23132,7 @@
         <v>44965</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>45625</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>46149</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23351,7 +23351,7 @@
         <v>45167</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>46150</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23502,7 +23502,7 @@
         <v>46150</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>44489</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         <v>46154</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
         <v>45341</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>45569</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23872,7 +23872,7 @@
         <v>45022</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23945,7 +23945,7 @@
         <v>45341</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>45453</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24091,7 +24091,7 @@
         <v>46161</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>45666</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>45322</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24315,7 +24315,7 @@
         <v>45876</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24393,7 +24393,7 @@
         <v>45268</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24466,7 +24466,7 @@
         <v>46162</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24544,7 +24544,7 @@
         <v>45876</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24622,7 +24622,7 @@
         <v>45461</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24695,7 +24695,7 @@
         <v>45313</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>44595</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>44595</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>45302</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>46170</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>44855</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>46171</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>45636</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25294,7 +25294,7 @@
         <v>46175</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25367,7 +25367,7 @@
         <v>45478</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25440,7 +25440,7 @@
         <v>45478</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25513,7 +25513,7 @@
         <v>45315</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25586,7 +25586,7 @@
         <v>45622</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25659,7 +25659,7 @@
         <v>44746</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>45600</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25805,7 +25805,7 @@
         <v>46037</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         <v>44941</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>46190</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>46190</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26097,7 +26097,7 @@
         <v>45121</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>45198</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26243,7 +26243,7 @@
         <v>45625</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26316,7 +26316,7 @@
         <v>45450</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26394,7 +26394,7 @@
         <v>45593</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26467,7 +26467,7 @@
         <v>45749</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26540,7 +26540,7 @@
         <v>45110</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26613,7 +26613,7 @@
         <v>44831</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26686,7 +26686,7 @@
         <v>45460</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26759,7 +26759,7 @@
         <v>45401</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26832,7 +26832,7 @@
         <v>46205</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>46205</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         <v>44918</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27056,7 +27056,7 @@
         <v>45176</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27134,7 +27134,7 @@
         <v>45243</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>45243</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>45243</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27353,7 +27353,7 @@
         <v>45686</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27426,7 +27426,7 @@
         <v>45302</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>44722</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27572,7 +27572,7 @@
         <v>44722</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>45002</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27718,7 +27718,7 @@
         <v>44677</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>45202</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>45097</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27937,7 +27937,7 @@
         <v>45302</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28010,7 +28010,7 @@
         <v>45393</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28083,7 +28083,7 @@
         <v>45239</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28156,7 +28156,7 @@
         <v>45058</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28234,7 +28234,7 @@
         <v>45442</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28307,7 +28307,7 @@
         <v>45226</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>45226</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28453,7 +28453,7 @@
         <v>45260</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>45679</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28599,7 +28599,7 @@
         <v>45379</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>45379</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28745,7 +28745,7 @@
         <v>46230</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28818,7 +28818,7 @@
         <v>46274</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28891,7 +28891,7 @@
         <v>46274</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28964,7 +28964,7 @@
         <v>46281</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29037,7 +29037,7 @@
         <v>46281</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29115,7 +29115,7 @@
         <v>44883</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29188,7 +29188,7 @@
         <v>45188</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         <v>46282</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29334,7 +29334,7 @@
         <v>45072</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>46282</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>46282</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29558,7 +29558,7 @@
         <v>44985</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29631,7 +29631,7 @@
         <v>46286</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29709,7 +29709,7 @@
         <v>45202</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>44851</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29860,7 +29860,7 @@
         <v>45181</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29938,7 +29938,7 @@
         <v>45082</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30011,7 +30011,7 @@
         <v>44637</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30084,7 +30084,7 @@
         <v>45513</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>45141</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30230,7 +30230,7 @@
         <v>45386</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         <v>44749</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30376,7 +30376,7 @@
         <v>44985</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30449,7 +30449,7 @@
         <v>45202</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>44987</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>44924</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>45201</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30741,7 +30741,7 @@
         <v>45098</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>46293</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30887,7 +30887,7 @@
         <v>45377</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30960,7 +30960,7 @@
         <v>45104</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>45366</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31106,7 +31106,7 @@
         <v>45267</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
         <v>45266</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31252,7 +31252,7 @@
         <v>45656</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31325,7 +31325,7 @@
         <v>44490</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31398,7 +31398,7 @@
         <v>45323</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31471,7 +31471,7 @@
         <v>44651</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31544,7 +31544,7 @@
         <v>46287</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31617,7 +31617,7 @@
         <v>45379</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31690,7 +31690,7 @@
         <v>45644</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31763,7 +31763,7 @@
         <v>44722</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>46213</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>45685</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31982,7 +31982,7 @@
         <v>45705</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>45119</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32128,7 +32128,7 @@
         <v>44533</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32201,7 +32201,7 @@
         <v>44847</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>45595</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32347,7 +32347,7 @@
         <v>45081</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>45701</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>44994</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>45243</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>44480</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32722,7 +32722,7 @@
         <v>45315</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32795,7 +32795,7 @@
         <v>45344</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>45282</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>45243</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33019,7 +33019,7 @@
         <v>45243</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33092,7 +33092,7 @@
         <v>45118</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33165,7 +33165,7 @@
         <v>45769</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33243,7 +33243,7 @@
         <v>45159</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33321,7 +33321,7 @@
         <v>44888</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33394,7 +33394,7 @@
         <v>44722</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33467,7 +33467,7 @@
         <v>45379</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>45478</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33613,7 +33613,7 @@
         <v>44770</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33686,7 +33686,7 @@
         <v>45701</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33764,7 +33764,7 @@
         <v>45783</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33842,7 +33842,7 @@
         <v>45636</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>43980</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>45247</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34064,7 +34064,7 @@
         <v>45247</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34142,7 +34142,7 @@
         <v>44657</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>45103</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34288,7 +34288,7 @@
         <v>44711</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34361,7 +34361,7 @@
         <v>45442</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34434,7 +34434,7 @@
         <v>45463</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34512,7 +34512,7 @@
         <v>45475</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34585,7 +34585,7 @@
         <v>45533</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34658,7 +34658,7 @@
         <v>44690</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>45442</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>44985</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34877,7 +34877,7 @@
         <v>45414</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>45442</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>45533</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35096,7 +35096,7 @@
         <v>45118</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35169,7 +35169,7 @@
         <v>45247</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>45512</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35320,7 +35320,7 @@
         <v>45783</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35398,7 +35398,7 @@
         <v>45792</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35476,7 +35476,7 @@
         <v>45805</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35554,7 +35554,7 @@
         <v>46040</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35627,7 +35627,7 @@
         <v>46106</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35705,7 +35705,7 @@
         <v>46036</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>

--- a/Översikt KRISTINEHAMN.xlsx
+++ b/Översikt KRISTINEHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45229</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45229</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45727</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>45118</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45265</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>44488</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>45091</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>45561</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>45562</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>45113</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>44690</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>45233</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>44525</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>44769</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>44574</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44614</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>44525</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>45002</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>45693</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>45380</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>44584</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>45674</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>45637</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>45804</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>45356</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>45819</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>45960</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>45960</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>44843</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>45982</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>46101</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>46101</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>44883</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>46000</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>45154</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>46141</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>45996</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>44337</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>44693</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>45579</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>45247</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>45716</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>45812</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>44831</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>44659</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>44683</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>44634</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>44734</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>44851</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>44559</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>44497</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>44536</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>44741</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>44576</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>44791</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>44588</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44588</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>44769</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>44829</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>44834</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>44657</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>44497</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>44518</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>44591</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>44573</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>44707</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>44518</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>44518</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>44501</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
         <v>44662</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         <v>44741</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>44742</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         <v>44551</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>44810</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>44501</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>44855</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>44584</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v>44825</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>44880</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>44706</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         <v>44657</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>44707</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         <v>44525</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>44706</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>44853</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>45450</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         <v>45366</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         <v>45072</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>45625</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>44923</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>45272</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>45167</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>45167</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>45265</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>45081</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>44972</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>45095</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>44742</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>45068</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>45202</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>45401</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>45208</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>45377</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>45202</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>45141</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>45313</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>45429</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>45282</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>45679</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>44994</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>45447</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>45110</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>45243</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>45243</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>44855</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>45393</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>45202</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>44888</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>45081</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>45252</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>44770</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>45315</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>45238</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
         <v>44497</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>45243</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>45379</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>45379</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         <v>44985</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>45387</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>45167</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>45323</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>44985</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>44883</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>44991</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>45631</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>44742</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>45268</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>45477</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>44941</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>45243</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>45705</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>45246</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
         <v>45513</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>45734</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>45324</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>45202</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12813,7 +12813,7 @@
         <v>44959</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>45222</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>45379</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>45636</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>45902</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13188,7 +13188,7 @@
         <v>45904</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>45679</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>44851</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>44656</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>44917</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>45905</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         <v>45392</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>45000</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13777,7 +13777,7 @@
         <v>44918</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
         <v>45685</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13928,7 +13928,7 @@
         <v>45110</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>45461</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>45593</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>45456</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>45366</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         <v>45121</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>45783</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>45644</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>44490</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>45079</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>44917</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>45188</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>45442</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>45595</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         <v>45622</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>45359</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15101,7 +15101,7 @@
         <v>44588</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>44588</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>45600</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15325,7 +15325,7 @@
         <v>45636</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15398,7 +15398,7 @@
         <v>45803</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>44677</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>44974</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>45792</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15700,7 +15700,7 @@
         <v>45792</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15778,7 +15778,7 @@
         <v>45792</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15856,7 +15856,7 @@
         <v>44805</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15929,7 +15929,7 @@
         <v>45082</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>45268</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16075,7 +16075,7 @@
         <v>45478</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>45792</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>45370</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>45379</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>45686</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16445,7 +16445,7 @@
         <v>45282</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16518,7 +16518,7 @@
         <v>45407</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>45700</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>45450</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16742,7 +16742,7 @@
         <v>45553</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         <v>45575</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>45798</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>44648</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>45933</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>45198</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>45625</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>45799</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>44722</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>44637</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>45802</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>45453</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>45805</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>45805</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>45044</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>45313</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>45810</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>45810</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>45812</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>45456</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>45944</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18300,7 +18300,7 @@
         <v>44812</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>45812</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>45239</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>44722</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>44722</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>44734</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>45041</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>44722</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18889,7 +18889,7 @@
         <v>44722</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>45267</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>45820</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>44753</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>45361</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>45364</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>45364</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>45378</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>45385</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>45600</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>45666</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>45364</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>45827</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>45181</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19916,7 +19916,7 @@
         <v>45202</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19989,7 +19989,7 @@
         <v>45952</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>45954</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>45118</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>45959</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>45769</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>45243</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>45833</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>45058</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20593,7 +20593,7 @@
         <v>45833</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>45832</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>45961</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20817,7 +20817,7 @@
         <v>44712</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>45833</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20963,7 +20963,7 @@
         <v>45664</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21036,7 +21036,7 @@
         <v>44749</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21109,7 +21109,7 @@
         <v>45961</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>45701</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
         <v>45662</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>44924</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>45119</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>45631</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21557,7 +21557,7 @@
         <v>45141</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>45749</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>45191</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
         <v>45201</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>45202</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>45701</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22000,7 +22000,7 @@
         <v>45302</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>45159</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22151,7 +22151,7 @@
         <v>45974</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>45315</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>45666</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22370,7 +22370,7 @@
         <v>45770</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22443,7 +22443,7 @@
         <v>45782</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>45344</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>44831</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>45656</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>45442</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>45097</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>45202</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>44480</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>44987</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>45303</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>45379</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>45647</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>45002</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>44965</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>45176</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23548,7 +23548,7 @@
         <v>45686</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23621,7 +23621,7 @@
         <v>45876</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>45876</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>44894</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>46094</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>46094</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>46094</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>44533</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24157,7 +24157,7 @@
         <v>45244</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24230,7 +24230,7 @@
         <v>46101</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24308,7 +24308,7 @@
         <v>46101</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24386,7 +24386,7 @@
         <v>45681</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>45678</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24537,7 +24537,7 @@
         <v>46106</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>44917</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>45260</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24761,7 +24761,7 @@
         <v>46107</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24834,7 +24834,7 @@
         <v>45386</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24907,7 +24907,7 @@
         <v>45302</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24980,7 +24980,7 @@
         <v>45253</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25053,7 +25053,7 @@
         <v>45681</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25131,7 +25131,7 @@
         <v>44847</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>45226</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>45226</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25350,7 +25350,7 @@
         <v>45076</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25423,7 +25423,7 @@
         <v>45995</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25496,7 +25496,7 @@
         <v>45995</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25569,7 +25569,7 @@
         <v>46000</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>45999</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>46000</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>45999</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>45999</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25959,7 +25959,7 @@
         <v>45999</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26037,7 +26037,7 @@
         <v>46001</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>45477</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26183,7 +26183,7 @@
         <v>45112</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>46129</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26339,7 +26339,7 @@
         <v>46129</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>45112</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>45268</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26568,7 +26568,7 @@
         <v>46132</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>44651</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>44841</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26787,7 +26787,7 @@
         <v>46003</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26860,7 +26860,7 @@
         <v>44741</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>46003</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27011,7 +27011,7 @@
         <v>45302</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27084,7 +27084,7 @@
         <v>46006</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>46009</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>46009</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>45203</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>45460</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>45887</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
         <v>45904</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>45888</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>45811</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>45222</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>44489</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>45888</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>46140</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>46034</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28111,7 +28111,7 @@
         <v>46139</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>45478</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28257,7 +28257,7 @@
         <v>45478</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>45933</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28403,7 +28403,7 @@
         <v>46034</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>45098</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>46036</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>45098</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>45701</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28773,7 +28773,7 @@
         <v>44526</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28846,7 +28846,7 @@
         <v>44526</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28919,7 +28919,7 @@
         <v>46038</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>46038</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29065,7 +29065,7 @@
         <v>46038</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>45104</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29211,7 +29211,7 @@
         <v>44595</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>44595</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29367,7 +29367,7 @@
         <v>45804</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>46136</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29513,7 +29513,7 @@
         <v>46140</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>45756</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>46048</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29742,7 +29742,7 @@
         <v>45999</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29820,7 +29820,7 @@
         <v>45243</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29893,7 +29893,7 @@
         <v>45243</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29966,7 +29966,7 @@
         <v>45243</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
         <v>45322</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>45127</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
         <v>45266</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30258,7 +30258,7 @@
         <v>44978</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
         <v>44746</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30404,7 +30404,7 @@
         <v>45639</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>46141</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30555,7 +30555,7 @@
         <v>46049</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30628,7 +30628,7 @@
         <v>46141</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>46051</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>45827</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>46141</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>46150</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>46149</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>46150</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31159,7 +31159,7 @@
         <v>46154</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31232,7 +31232,7 @@
         <v>46083</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31310,7 +31310,7 @@
         <v>45022</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>45341</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>45341</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>45569</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>46092</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>46161</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>46092</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>46092</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31914,7 +31914,7 @@
         <v>46162</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31992,7 +31992,7 @@
         <v>46170</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32065,7 +32065,7 @@
         <v>46171</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>46175</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32216,7 +32216,7 @@
         <v>46037</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>46190</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32362,7 +32362,7 @@
         <v>46190</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         <v>46205</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>46205</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32581,7 +32581,7 @@
         <v>46274</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>46274</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>46230</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32800,7 +32800,7 @@
         <v>46282</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>46281</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>46281</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33024,7 +33024,7 @@
         <v>46282</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33097,7 +33097,7 @@
         <v>46282</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33170,7 +33170,7 @@
         <v>46286</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>46293</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33321,7 +33321,7 @@
         <v>46213</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33394,7 +33394,7 @@
         <v>46287</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33467,7 +33467,7 @@
         <v>46302</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>46142</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33616,7 +33616,7 @@
         <v>43980</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33689,7 +33689,7 @@
         <v>44657</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33762,7 +33762,7 @@
         <v>44711</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>44690</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>45247</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>45247</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34064,7 +34064,7 @@
         <v>45103</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>45442</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>45463</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34288,7 +34288,7 @@
         <v>45475</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34361,7 +34361,7 @@
         <v>45533</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34434,7 +34434,7 @@
         <v>45442</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34507,7 +34507,7 @@
         <v>44985</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34580,7 +34580,7 @@
         <v>45414</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>45442</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>45533</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34799,7 +34799,7 @@
         <v>45118</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34872,7 +34872,7 @@
         <v>45247</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>45512</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>45783</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35101,7 +35101,7 @@
         <v>45792</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35179,7 +35179,7 @@
         <v>45805</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35257,7 +35257,7 @@
         <v>46040</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35330,7 +35330,7 @@
         <v>46106</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35408,7 +35408,7 @@
         <v>46036</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>

--- a/Översikt KRISTINEHAMN.xlsx
+++ b/Översikt KRISTINEHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45229</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45229</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45727</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>45118</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45265</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>44488</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>45091</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>45561</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>45562</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>45113</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>44690</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>45233</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>44525</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>44769</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>44574</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44614</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>44525</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>45002</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>45693</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>45380</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>44584</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>45674</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>45637</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>45804</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>45356</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>45819</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>45960</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>45960</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>44843</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>45982</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>46101</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>46101</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>44883</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>46000</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>45154</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>46141</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>45996</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>44337</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>44693</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>45579</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>45247</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>45716</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>45812</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>44831</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>44659</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>44683</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>44634</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>44734</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>44851</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>44559</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>44497</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>44536</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>44741</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>44576</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>44791</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>44588</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44588</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>44769</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>44829</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>44834</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>44657</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>44497</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>44518</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>44591</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>44573</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>44707</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>44518</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>44518</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>44501</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
         <v>44662</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         <v>44741</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>44742</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         <v>44551</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>44810</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>44501</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>44855</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>44584</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v>44825</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>44880</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>44706</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         <v>44657</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>44707</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         <v>44525</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>44706</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>44853</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>45450</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         <v>45366</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         <v>45072</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>45625</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>44923</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>45272</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>45167</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>45167</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>45265</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>45081</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>44972</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>45095</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>44742</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>45068</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>45202</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>45401</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>45208</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>45377</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>45202</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>45141</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>45313</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>45429</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>45282</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>45679</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>44994</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>45447</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>45110</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>45243</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>45243</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>44855</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>45393</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>45202</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>44888</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>45081</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>45252</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>44770</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>45315</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>45238</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
         <v>44497</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>45243</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>45379</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>45379</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         <v>44985</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>45387</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>45167</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>45323</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>44985</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>44883</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>44991</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>45631</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>44742</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>45268</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>45477</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>44941</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>45243</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>45705</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>45246</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
         <v>45513</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>45734</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>45324</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>45202</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12813,7 +12813,7 @@
         <v>44959</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>45222</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>45379</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>45636</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>45902</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13188,7 +13188,7 @@
         <v>45904</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>45679</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>44851</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>44656</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>44917</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>45905</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         <v>45392</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>45000</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13777,7 +13777,7 @@
         <v>44918</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
         <v>45685</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13928,7 +13928,7 @@
         <v>45110</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>45461</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>45593</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>45456</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>45366</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         <v>45121</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>45783</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>45644</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>44490</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>45079</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>44917</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>45188</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>45442</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>45595</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         <v>45622</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>45359</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15101,7 +15101,7 @@
         <v>44588</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>44588</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>45600</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15325,7 +15325,7 @@
         <v>45636</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15398,7 +15398,7 @@
         <v>45803</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>44677</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>44974</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>45792</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15700,7 +15700,7 @@
         <v>45792</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15778,7 +15778,7 @@
         <v>45792</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15856,7 +15856,7 @@
         <v>44805</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15929,7 +15929,7 @@
         <v>45082</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>45268</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16075,7 +16075,7 @@
         <v>45478</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>45792</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>45370</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>45379</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>45686</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16445,7 +16445,7 @@
         <v>45282</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16518,7 +16518,7 @@
         <v>45407</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>45700</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>45450</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16742,7 +16742,7 @@
         <v>45553</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         <v>45575</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>45798</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>44648</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>45933</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>45198</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>45625</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>45799</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>44722</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>44637</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>45802</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>45453</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>45805</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>45805</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>45044</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>45313</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>45810</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>45810</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>45812</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>45456</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>45944</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18300,7 +18300,7 @@
         <v>44812</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>45812</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>45239</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>44722</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>44722</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>44734</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>45041</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>44722</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18889,7 +18889,7 @@
         <v>44722</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>45267</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>45820</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>44753</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>45361</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>45364</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>45364</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>45378</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>45385</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>45600</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>45666</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>45364</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>45827</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>45181</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19916,7 +19916,7 @@
         <v>45202</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19989,7 +19989,7 @@
         <v>45952</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>45954</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>45118</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>45959</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>45769</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>45243</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>45833</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>45058</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20593,7 +20593,7 @@
         <v>45833</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>45832</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>45961</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20817,7 +20817,7 @@
         <v>44712</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>45833</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20963,7 +20963,7 @@
         <v>45664</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21036,7 +21036,7 @@
         <v>44749</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21109,7 +21109,7 @@
         <v>45961</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>45701</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
         <v>45662</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>44924</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>45119</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>45631</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21557,7 +21557,7 @@
         <v>45141</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>45749</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>45191</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
         <v>45201</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>45202</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>45701</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22000,7 +22000,7 @@
         <v>45302</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>45159</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22151,7 +22151,7 @@
         <v>45974</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>45315</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>45666</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22370,7 +22370,7 @@
         <v>45770</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22443,7 +22443,7 @@
         <v>45782</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>45344</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>44831</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>45656</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>45442</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>45097</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>45202</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>44480</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>44987</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>45303</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>45379</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>45647</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>45002</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>44965</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>45176</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23548,7 +23548,7 @@
         <v>45686</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23621,7 +23621,7 @@
         <v>45876</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>45876</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>44894</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>46094</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>46094</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>46094</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>44533</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24157,7 +24157,7 @@
         <v>45244</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24230,7 +24230,7 @@
         <v>46101</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24308,7 +24308,7 @@
         <v>46101</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24386,7 +24386,7 @@
         <v>45681</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>45678</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24537,7 +24537,7 @@
         <v>46106</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>44917</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>45260</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24761,7 +24761,7 @@
         <v>46107</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24834,7 +24834,7 @@
         <v>45386</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24907,7 +24907,7 @@
         <v>45302</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24980,7 +24980,7 @@
         <v>45253</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25053,7 +25053,7 @@
         <v>45681</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25131,7 +25131,7 @@
         <v>44847</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>45226</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>45226</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25350,7 +25350,7 @@
         <v>45076</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25423,7 +25423,7 @@
         <v>45995</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25496,7 +25496,7 @@
         <v>45995</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25569,7 +25569,7 @@
         <v>46000</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>45999</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>46000</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>45999</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>45999</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25959,7 +25959,7 @@
         <v>45999</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26037,7 +26037,7 @@
         <v>46001</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>45477</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26183,7 +26183,7 @@
         <v>45112</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>46129</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26339,7 +26339,7 @@
         <v>46129</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>45112</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>45268</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26568,7 +26568,7 @@
         <v>46132</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>44651</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>44841</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26787,7 +26787,7 @@
         <v>46003</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26860,7 +26860,7 @@
         <v>44741</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>46003</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27011,7 +27011,7 @@
         <v>45302</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27084,7 +27084,7 @@
         <v>46006</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>46009</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>46009</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>45203</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>45460</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>45887</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
         <v>45904</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>45888</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>45811</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>45222</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>44489</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>45888</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>46140</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>46034</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28111,7 +28111,7 @@
         <v>46139</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>45478</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28257,7 +28257,7 @@
         <v>45478</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>45933</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28403,7 +28403,7 @@
         <v>46034</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>45098</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>46036</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>45098</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>45701</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28773,7 +28773,7 @@
         <v>44526</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28846,7 +28846,7 @@
         <v>44526</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28919,7 +28919,7 @@
         <v>46038</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>46038</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29065,7 +29065,7 @@
         <v>46038</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>45104</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29211,7 +29211,7 @@
         <v>44595</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>44595</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29367,7 +29367,7 @@
         <v>45804</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>46136</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29513,7 +29513,7 @@
         <v>46140</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>45756</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>46048</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29742,7 +29742,7 @@
         <v>45999</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29820,7 +29820,7 @@
         <v>45243</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29893,7 +29893,7 @@
         <v>45243</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29966,7 +29966,7 @@
         <v>45243</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
         <v>45322</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>45127</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
         <v>45266</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30258,7 +30258,7 @@
         <v>44978</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
         <v>44746</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30404,7 +30404,7 @@
         <v>45639</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>46141</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30555,7 +30555,7 @@
         <v>46049</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30628,7 +30628,7 @@
         <v>46141</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>46051</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>45827</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>46141</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>46150</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>46149</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>46150</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31159,7 +31159,7 @@
         <v>46154</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31232,7 +31232,7 @@
         <v>46083</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31310,7 +31310,7 @@
         <v>45022</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>45341</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>45341</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>45569</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>46092</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>46161</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>46092</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>46092</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31914,7 +31914,7 @@
         <v>46162</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31992,7 +31992,7 @@
         <v>46170</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32065,7 +32065,7 @@
         <v>46171</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>46175</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32216,7 +32216,7 @@
         <v>46037</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>46190</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32362,7 +32362,7 @@
         <v>46190</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         <v>46205</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>46205</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32581,7 +32581,7 @@
         <v>46274</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>46274</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>46230</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32800,7 +32800,7 @@
         <v>46282</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>46281</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>46281</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33024,7 +33024,7 @@
         <v>46282</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33097,7 +33097,7 @@
         <v>46282</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33170,7 +33170,7 @@
         <v>46286</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>46293</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33321,7 +33321,7 @@
         <v>46213</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33394,7 +33394,7 @@
         <v>46287</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33467,7 +33467,7 @@
         <v>46302</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>46142</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33616,7 +33616,7 @@
         <v>43980</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33689,7 +33689,7 @@
         <v>44657</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33762,7 +33762,7 @@
         <v>44711</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>44690</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>45247</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>45247</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34064,7 +34064,7 @@
         <v>45103</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>45442</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>45463</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34288,7 +34288,7 @@
         <v>45475</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34361,7 +34361,7 @@
         <v>45533</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34434,7 +34434,7 @@
         <v>45442</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34507,7 +34507,7 @@
         <v>44985</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34580,7 +34580,7 @@
         <v>45414</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>45442</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>45533</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34799,7 +34799,7 @@
         <v>45118</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34872,7 +34872,7 @@
         <v>45247</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>45512</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>45783</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35101,7 +35101,7 @@
         <v>45792</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35179,7 +35179,7 @@
         <v>45805</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35257,7 +35257,7 @@
         <v>46040</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35330,7 +35330,7 @@
         <v>46106</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35408,7 +35408,7 @@
         <v>46036</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>

--- a/Översikt KRISTINEHAMN.xlsx
+++ b/Översikt KRISTINEHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45229</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45229</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45727</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>45118</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45265</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>44488</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>45091</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>45561</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>45562</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>45113</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>45233</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>44690</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>44525</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>44769</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>44574</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44525</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>44614</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>45002</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>45637</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>45693</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>44584</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>45356</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>46141</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>44883</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>45960</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>45960</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>45380</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>45982</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>46000</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45996</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>45154</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>44843</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>46101</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>46101</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>45674</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>45804</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>45819</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>44337</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>45579</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>44693</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>45247</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>45716</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>45812</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>44831</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>44683</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>44634</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>44734</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>44659</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>44851</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>44559</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>44497</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>44536</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>44741</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>44791</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>44576</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>44588</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44588</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>44769</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>44829</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>44834</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>44657</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>44497</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>44518</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>44551</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>44501</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>44657</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>44662</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>44707</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>44742</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>44810</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         <v>44880</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>44853</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>44573</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>44855</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>44706</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>44591</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>44518</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v>44518</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>44501</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>44741</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         <v>44584</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>44825</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         <v>44707</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>44706</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>45631</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>44841</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>45442</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>45324</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>45141</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>45081</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>44525</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
         <v>44991</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         <v>45095</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>44974</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>45734</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         <v>45272</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>44894</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>45238</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>44722</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         <v>45222</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>45456</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
         <v>45600</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>45202</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>44959</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>45222</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>45447</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>45662</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>45110</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>44588</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>45701</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>45268</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>45244</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>45044</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>44812</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>44917</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>45303</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>44741</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>45253</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>44917</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>45246</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>45202</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>44742</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>44742</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>45202</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>45370</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>45000</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>45041</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>45429</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>45678</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>45243</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>45456</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>45666</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>45167</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>44588</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>45167</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>45191</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>45243</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
         <v>44734</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         <v>45313</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>45647</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>45999</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>45933</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
         <v>44497</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>45202</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>45756</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>44917</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>45387</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>45770</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>45887</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>45477</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>46139</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13188,7 +13188,7 @@
         <v>45252</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>45208</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>45904</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>46140</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>46141</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>46141</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
         <v>46141</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>46140</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13797,7 +13797,7 @@
         <v>45902</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>45127</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13948,7 +13948,7 @@
         <v>44656</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14021,7 +14021,7 @@
         <v>45203</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14094,7 +14094,7 @@
         <v>45905</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>45904</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
         <v>45827</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         <v>45076</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>45888</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14459,7 +14459,7 @@
         <v>45079</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>45681</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>45366</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>44648</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14756,7 +14756,7 @@
         <v>45681</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
         <v>45265</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>45379</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>44978</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>45803</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>46149</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>46150</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15287,7 +15287,7 @@
         <v>45933</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15360,7 +15360,7 @@
         <v>45361</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>46150</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         <v>45944</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>45098</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>45392</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         <v>45679</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>45450</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>44526</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>44526</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>44712</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>46154</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>45341</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>45952</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16319,7 +16319,7 @@
         <v>45639</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>45569</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>45022</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16538,7 +16538,7 @@
         <v>45068</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16611,7 +16611,7 @@
         <v>45631</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16684,7 +16684,7 @@
         <v>45341</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16757,7 +16757,7 @@
         <v>44753</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>45477</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>45954</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>45959</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>44923</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>44972</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>45961</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>45961</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>45268</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>46161</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>45359</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>45974</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>45625</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>45167</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17804,7 +17804,7 @@
         <v>46162</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>44489</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>45453</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18028,7 +18028,7 @@
         <v>45666</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18101,7 +18101,7 @@
         <v>45995</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>45322</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>45995</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>45268</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>45999</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>45999</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>45999</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>45999</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>46001</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>46170</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>45461</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>46000</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>46000</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>45313</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>44595</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19231,7 +19231,7 @@
         <v>44595</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19309,7 +19309,7 @@
         <v>46003</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>46003</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>46006</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>45302</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>46009</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>46171</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19752,7 +19752,7 @@
         <v>44855</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19825,7 +19825,7 @@
         <v>46009</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19898,7 +19898,7 @@
         <v>45636</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19971,7 +19971,7 @@
         <v>45478</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20044,7 +20044,7 @@
         <v>45478</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20117,7 +20117,7 @@
         <v>45315</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20190,7 +20190,7 @@
         <v>45622</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20263,7 +20263,7 @@
         <v>44746</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>45600</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>46034</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>46034</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20555,7 +20555,7 @@
         <v>46175</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20628,7 +20628,7 @@
         <v>46036</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>46038</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20774,7 +20774,7 @@
         <v>46038</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20847,7 +20847,7 @@
         <v>46038</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>44941</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20993,7 +20993,7 @@
         <v>46049</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>45121</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21139,7 +21139,7 @@
         <v>46048</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21212,7 +21212,7 @@
         <v>46051</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>45198</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>45625</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>45450</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>45593</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>46037</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>45749</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>45110</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>44831</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>45460</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21947,7 +21947,7 @@
         <v>45401</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>46083</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22098,7 +22098,7 @@
         <v>44918</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22176,7 +22176,7 @@
         <v>45176</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22254,7 +22254,7 @@
         <v>46190</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22327,7 +22327,7 @@
         <v>46190</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22400,7 +22400,7 @@
         <v>46092</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22478,7 +22478,7 @@
         <v>46092</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         <v>46092</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22634,7 +22634,7 @@
         <v>46094</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22712,7 +22712,7 @@
         <v>46094</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22790,7 +22790,7 @@
         <v>46094</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>45243</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>45243</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>45243</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>45686</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23160,7 +23160,7 @@
         <v>45302</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23233,7 +23233,7 @@
         <v>44722</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>44722</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23379,7 +23379,7 @@
         <v>45002</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23452,7 +23452,7 @@
         <v>44677</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23525,7 +23525,7 @@
         <v>45202</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>46101</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23676,7 +23676,7 @@
         <v>46101</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>45097</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>45302</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23900,7 +23900,7 @@
         <v>46106</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>46107</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>45393</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>45239</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24197,7 +24197,7 @@
         <v>45058</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24275,7 +24275,7 @@
         <v>45442</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>45226</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24421,7 +24421,7 @@
         <v>45226</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24494,7 +24494,7 @@
         <v>45112</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>46129</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24650,7 +24650,7 @@
         <v>45112</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24728,7 +24728,7 @@
         <v>46132</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         <v>45260</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
         <v>45679</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>45379</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>45379</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>45804</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>45888</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>46205</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>46205</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         <v>46136</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>45811</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>44883</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>45188</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>45072</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25755,7 +25755,7 @@
         <v>44985</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>45202</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25901,7 +25901,7 @@
         <v>44851</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>45181</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>45082</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>44637</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26203,7 +26203,7 @@
         <v>45513</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>45141</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>45386</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>44749</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>46230</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26568,7 +26568,7 @@
         <v>44985</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>45202</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>44987</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26787,7 +26787,7 @@
         <v>46274</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26860,7 +26860,7 @@
         <v>46274</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26933,7 +26933,7 @@
         <v>44924</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         <v>45201</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>45098</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>45377</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>45104</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27298,7 +27298,7 @@
         <v>46281</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27371,7 +27371,7 @@
         <v>45366</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27444,7 +27444,7 @@
         <v>45267</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27517,7 +27517,7 @@
         <v>46281</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>45266</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>45656</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>44490</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>45323</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>44651</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>45379</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>46282</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>46282</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>46282</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28252,7 +28252,7 @@
         <v>45644</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>44722</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28398,7 +28398,7 @@
         <v>46286</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>45685</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>45705</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>45119</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>44533</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>44847</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>45595</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
         <v>45081</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>45701</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29065,7 +29065,7 @@
         <v>44994</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         <v>46293</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>45243</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>45315</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>45344</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>45282</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29513,7 +29513,7 @@
         <v>45243</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29586,7 +29586,7 @@
         <v>45243</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29659,7 +29659,7 @@
         <v>45118</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29732,7 +29732,7 @@
         <v>45769</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>45159</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29888,7 +29888,7 @@
         <v>44888</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29961,7 +29961,7 @@
         <v>46287</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30034,7 +30034,7 @@
         <v>44722</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>45379</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30180,7 +30180,7 @@
         <v>46213</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30253,7 +30253,7 @@
         <v>45478</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>44770</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30399,7 +30399,7 @@
         <v>45701</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>45783</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30555,7 +30555,7 @@
         <v>45636</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30628,7 +30628,7 @@
         <v>46302</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30701,7 +30701,7 @@
         <v>44805</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>45792</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>45792</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>45792</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>45792</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>45700</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31159,7 +31159,7 @@
         <v>45686</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31232,7 +31232,7 @@
         <v>45407</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>45282</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31378,7 +31378,7 @@
         <v>45799</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>45575</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>45553</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>45798</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>45802</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31753,7 +31753,7 @@
         <v>45805</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>45805</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>45810</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31982,7 +31982,7 @@
         <v>45810</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>45812</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32133,7 +32133,7 @@
         <v>45812</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32211,7 +32211,7 @@
         <v>45820</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>46307</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32357,7 +32357,7 @@
         <v>45364</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32430,7 +32430,7 @@
         <v>45385</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32503,7 +32503,7 @@
         <v>45827</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>45378</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>45364</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32722,7 +32722,7 @@
         <v>45364</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32795,7 +32795,7 @@
         <v>45833</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32868,7 +32868,7 @@
         <v>45832</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32941,7 +32941,7 @@
         <v>45833</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33014,7 +33014,7 @@
         <v>45833</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33087,7 +33087,7 @@
         <v>45664</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33160,7 +33160,7 @@
         <v>45782</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>44965</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33306,7 +33306,7 @@
         <v>45876</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>45876</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33460,7 +33460,7 @@
         <v>43980</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>45247</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>45247</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33689,7 +33689,7 @@
         <v>44657</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33762,7 +33762,7 @@
         <v>45103</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>44711</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>45442</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33981,7 +33981,7 @@
         <v>45463</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34059,7 +34059,7 @@
         <v>45475</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34132,7 +34132,7 @@
         <v>45533</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34205,7 +34205,7 @@
         <v>44690</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34278,7 +34278,7 @@
         <v>45442</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34351,7 +34351,7 @@
         <v>44985</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34424,7 +34424,7 @@
         <v>45414</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>45442</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34570,7 +34570,7 @@
         <v>45533</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34643,7 +34643,7 @@
         <v>45118</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>45247</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>45512</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34867,7 +34867,7 @@
         <v>45783</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34945,7 +34945,7 @@
         <v>45792</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>45805</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35101,7 +35101,7 @@
         <v>46040</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35174,7 +35174,7 @@
         <v>46106</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35252,7 +35252,7 @@
         <v>46036</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>

--- a/Översikt KRISTINEHAMN.xlsx
+++ b/Översikt KRISTINEHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45229</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45229</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45727</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>45118</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45265</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>44488</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>45091</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>45561</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>45562</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>45113</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>45233</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>44690</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>44525</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>44769</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>44574</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44525</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>44614</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>45002</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>45637</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>45693</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>44584</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>45356</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>46141</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>44883</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>45960</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>45960</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>45380</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>45982</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>46000</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45996</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>45154</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>44843</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>46101</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>46101</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>45674</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>45804</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>45819</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>44337</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>45579</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>44693</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>45247</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>45716</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>45812</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>44831</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>44683</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>44634</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>44734</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>44659</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>44851</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>44559</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>44497</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>44536</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>44741</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>44791</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>44576</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>44588</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44588</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>44769</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>44829</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>44834</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>44657</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>44497</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>44518</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>44551</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>44501</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>44657</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>44662</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>44707</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>44742</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>44810</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         <v>44880</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>44853</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>44573</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>44855</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>44706</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>44591</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>44518</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v>44518</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>44501</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>44741</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         <v>44584</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>44825</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         <v>44707</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>44706</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>45631</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>44841</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>45442</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>45324</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>45141</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>45081</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>44525</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
         <v>44991</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         <v>45095</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>44974</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>45734</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         <v>45272</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>44894</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>45238</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>44722</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         <v>45222</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>45456</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
         <v>45600</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>45202</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>44959</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>45222</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>45447</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>45662</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>45110</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>44588</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>45701</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>45268</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>45244</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>45044</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>44812</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>44917</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>45303</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>44741</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>45253</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>44917</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>45246</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>45202</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>44742</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>44742</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>45202</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>45370</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>45000</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>45041</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>45429</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>45678</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>45243</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>45456</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>45666</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>45167</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>44588</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>45167</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>45191</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>45243</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
         <v>44734</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         <v>45313</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>45647</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>45999</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>45933</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
         <v>44497</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>45202</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>45756</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>44917</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>45387</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>45770</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>45887</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>45477</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>46139</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13188,7 +13188,7 @@
         <v>45252</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>45208</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>45904</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>46140</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>46141</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>46141</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
         <v>46141</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>46140</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13797,7 +13797,7 @@
         <v>45902</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>45127</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13948,7 +13948,7 @@
         <v>44656</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14021,7 +14021,7 @@
         <v>45203</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14094,7 +14094,7 @@
         <v>45905</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>45904</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
         <v>45827</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         <v>45076</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>45888</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14459,7 +14459,7 @@
         <v>45079</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>45681</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>45366</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>44648</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14756,7 +14756,7 @@
         <v>45681</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
         <v>45265</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>45379</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>44978</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>45803</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>46149</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>46150</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15287,7 +15287,7 @@
         <v>45933</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15360,7 +15360,7 @@
         <v>45361</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>46150</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         <v>45944</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>45098</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>45392</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         <v>45679</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>45450</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>44526</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>44526</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>44712</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>46154</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>45341</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>45952</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16319,7 +16319,7 @@
         <v>45639</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>45569</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>45022</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16538,7 +16538,7 @@
         <v>45068</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16611,7 +16611,7 @@
         <v>45631</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16684,7 +16684,7 @@
         <v>45341</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16757,7 +16757,7 @@
         <v>44753</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>45477</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>45954</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>45959</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>44923</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>44972</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>45961</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>45961</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>45268</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>46161</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>45359</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>45974</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>45625</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>45167</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17804,7 +17804,7 @@
         <v>46162</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>44489</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>45453</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18028,7 +18028,7 @@
         <v>45666</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18101,7 +18101,7 @@
         <v>45995</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>45322</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>45995</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>45268</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>45999</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>45999</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>45999</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>45999</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>46001</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>46170</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>45461</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>46000</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>46000</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>45313</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>44595</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19231,7 +19231,7 @@
         <v>44595</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19309,7 +19309,7 @@
         <v>46003</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>46003</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>46006</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>45302</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>46009</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>46171</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19752,7 +19752,7 @@
         <v>44855</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19825,7 +19825,7 @@
         <v>46009</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19898,7 +19898,7 @@
         <v>45636</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19971,7 +19971,7 @@
         <v>45478</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20044,7 +20044,7 @@
         <v>45478</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20117,7 +20117,7 @@
         <v>45315</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20190,7 +20190,7 @@
         <v>45622</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20263,7 +20263,7 @@
         <v>44746</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>45600</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>46034</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>46034</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20555,7 +20555,7 @@
         <v>46175</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20628,7 +20628,7 @@
         <v>46036</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>46038</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20774,7 +20774,7 @@
         <v>46038</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20847,7 +20847,7 @@
         <v>46038</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>44941</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20993,7 +20993,7 @@
         <v>46049</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>45121</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21139,7 +21139,7 @@
         <v>46048</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21212,7 +21212,7 @@
         <v>46051</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>45198</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>45625</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>45450</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>45593</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>46037</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>45749</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>45110</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>44831</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>45460</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21947,7 +21947,7 @@
         <v>45401</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>46083</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22098,7 +22098,7 @@
         <v>44918</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22176,7 +22176,7 @@
         <v>45176</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22254,7 +22254,7 @@
         <v>46190</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22327,7 +22327,7 @@
         <v>46190</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22400,7 +22400,7 @@
         <v>46092</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22478,7 +22478,7 @@
         <v>46092</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         <v>46092</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22634,7 +22634,7 @@
         <v>46094</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22712,7 +22712,7 @@
         <v>46094</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22790,7 +22790,7 @@
         <v>46094</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>45243</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>45243</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>45243</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>45686</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23160,7 +23160,7 @@
         <v>45302</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23233,7 +23233,7 @@
         <v>44722</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>44722</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23379,7 +23379,7 @@
         <v>45002</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23452,7 +23452,7 @@
         <v>44677</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23525,7 +23525,7 @@
         <v>45202</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>46101</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23676,7 +23676,7 @@
         <v>46101</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>45097</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>45302</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23900,7 +23900,7 @@
         <v>46106</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>46107</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>45393</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>45239</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24197,7 +24197,7 @@
         <v>45058</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24275,7 +24275,7 @@
         <v>45442</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>45226</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24421,7 +24421,7 @@
         <v>45226</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24494,7 +24494,7 @@
         <v>45112</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>46129</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24650,7 +24650,7 @@
         <v>45112</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24728,7 +24728,7 @@
         <v>46132</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         <v>45260</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
         <v>45679</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>45379</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>45379</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>45804</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>45888</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>46205</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>46205</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         <v>46136</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>45811</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>44883</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>45188</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>45072</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25755,7 +25755,7 @@
         <v>44985</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>45202</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25901,7 +25901,7 @@
         <v>44851</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>45181</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>45082</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>44637</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26203,7 +26203,7 @@
         <v>45513</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>45141</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>45386</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>44749</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>46230</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26568,7 +26568,7 @@
         <v>44985</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>45202</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>44987</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26787,7 +26787,7 @@
         <v>46274</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26860,7 +26860,7 @@
         <v>46274</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26933,7 +26933,7 @@
         <v>44924</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         <v>45201</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>45098</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>45377</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>45104</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27298,7 +27298,7 @@
         <v>46281</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27371,7 +27371,7 @@
         <v>45366</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27444,7 +27444,7 @@
         <v>45267</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27517,7 +27517,7 @@
         <v>46281</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>45266</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>45656</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>44490</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>45323</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>44651</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>45379</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>46282</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>46282</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>46282</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28252,7 +28252,7 @@
         <v>45644</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>44722</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28398,7 +28398,7 @@
         <v>46286</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>45685</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>45705</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>45119</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>44533</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>44847</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>45595</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
         <v>45081</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>45701</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29065,7 +29065,7 @@
         <v>44994</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         <v>46293</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>45243</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>45315</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>45344</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>45282</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29513,7 +29513,7 @@
         <v>45243</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29586,7 +29586,7 @@
         <v>45243</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29659,7 +29659,7 @@
         <v>45118</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29732,7 +29732,7 @@
         <v>45769</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>45159</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29888,7 +29888,7 @@
         <v>44888</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29961,7 +29961,7 @@
         <v>46287</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30034,7 +30034,7 @@
         <v>44722</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>45379</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30180,7 +30180,7 @@
         <v>46213</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30253,7 +30253,7 @@
         <v>45478</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>44770</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30399,7 +30399,7 @@
         <v>45701</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>45783</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30555,7 +30555,7 @@
         <v>45636</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30628,7 +30628,7 @@
         <v>46302</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30701,7 +30701,7 @@
         <v>44805</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>45792</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>45792</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>45792</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>45792</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>45700</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31159,7 +31159,7 @@
         <v>45686</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31232,7 +31232,7 @@
         <v>45407</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>45282</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31378,7 +31378,7 @@
         <v>45799</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>45575</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>45553</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>45798</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>45802</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31753,7 +31753,7 @@
         <v>45805</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>45805</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>45810</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31982,7 +31982,7 @@
         <v>45810</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>45812</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32133,7 +32133,7 @@
         <v>45812</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32211,7 +32211,7 @@
         <v>45820</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>46307</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32357,7 +32357,7 @@
         <v>45364</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32430,7 +32430,7 @@
         <v>45385</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32503,7 +32503,7 @@
         <v>45827</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>45378</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>45364</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32722,7 +32722,7 @@
         <v>45364</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32795,7 +32795,7 @@
         <v>45833</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32868,7 +32868,7 @@
         <v>45832</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32941,7 +32941,7 @@
         <v>45833</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33014,7 +33014,7 @@
         <v>45833</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33087,7 +33087,7 @@
         <v>45664</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33160,7 +33160,7 @@
         <v>45782</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>44965</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33306,7 +33306,7 @@
         <v>45876</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>45876</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33460,7 +33460,7 @@
         <v>43980</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>45247</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>45247</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33689,7 +33689,7 @@
         <v>44657</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33762,7 +33762,7 @@
         <v>45103</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>44711</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>45442</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33981,7 +33981,7 @@
         <v>45463</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34059,7 +34059,7 @@
         <v>45475</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34132,7 +34132,7 @@
         <v>45533</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34205,7 +34205,7 @@
         <v>44690</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34278,7 +34278,7 @@
         <v>45442</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34351,7 +34351,7 @@
         <v>44985</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34424,7 +34424,7 @@
         <v>45414</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>45442</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34570,7 +34570,7 @@
         <v>45533</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34643,7 +34643,7 @@
         <v>45118</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>45247</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>45512</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34867,7 +34867,7 @@
         <v>45783</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34945,7 +34945,7 @@
         <v>45792</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>45805</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35101,7 +35101,7 @@
         <v>46040</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35174,7 +35174,7 @@
         <v>46106</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35252,7 +35252,7 @@
         <v>46036</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>

--- a/Översikt KRISTINEHAMN.xlsx
+++ b/Översikt KRISTINEHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45229</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45229</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45727</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>45118</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45265</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>45091</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45561</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>45562</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>45113</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>44690</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45233</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44525</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>44769</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>44574</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>44525</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>44614</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>45154</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>45960</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>45960</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>45982</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>45693</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>46000</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>45674</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>45804</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         <v>45996</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>45819</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>46101</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>46101</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>44584</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>46141</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>45637</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>44843</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>44883</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>45002</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>45380</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>45356</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>44337</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>44693</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>45579</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>45247</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>45716</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>45812</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>44831</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         <v>44659</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>44683</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>44634</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>44734</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>44559</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>44851</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>44497</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>44536</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>44741</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>44576</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>44791</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>44588</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6095,7 +6095,7 @@
         <v>44588</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>44769</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>44829</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>44834</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>44657</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>44518</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>44497</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>44551</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>44501</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>44657</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>44707</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>44662</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         <v>44742</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
         <v>44810</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>44880</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         <v>44853</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7263,7 +7263,7 @@
         <v>44573</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>44855</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         <v>44706</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         <v>44591</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>44518</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>44518</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>44501</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>44741</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>44584</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>44825</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         <v>44707</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         <v>44706</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>45625</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         <v>45302</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>45477</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>44742</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>45208</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         <v>45377</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>45202</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>45202</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>44770</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>45203</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>45460</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>45902</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>45904</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>45905</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>46161</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>46162</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>45222</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>45478</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>45478</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>45098</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>45098</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>45701</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>44526</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>44526</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>45104</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         <v>44595</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>44595</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         <v>45803</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10223,7 +10223,7 @@
         <v>46170</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>46171</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>45243</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         <v>45243</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         <v>45243</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
         <v>45933</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         <v>45322</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>45266</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>44978</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>44746</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
         <v>45639</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>45265</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         <v>45450</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>46175</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>45095</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>45944</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>45072</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11484,7 +11484,7 @@
         <v>45429</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>45282</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11630,7 +11630,7 @@
         <v>45447</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>45167</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>44855</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>45393</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>44888</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>44972</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>45952</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>46037</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>45068</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12287,7 +12287,7 @@
         <v>45202</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>45401</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12433,7 +12433,7 @@
         <v>45954</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>45141</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>45243</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>45243</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>45959</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>45961</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>45961</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>46190</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>45315</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>46190</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>45243</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>45167</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         <v>45323</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>45974</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>44985</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>44991</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13621,7 +13621,7 @@
         <v>45631</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>44742</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>45705</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>45734</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         <v>45202</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>46205</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>46205</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>45222</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>45379</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>45636</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>44883</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         <v>45679</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>45995</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>45995</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>46000</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>45999</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14804,7 +14804,7 @@
         <v>46000</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>45685</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         <v>45999</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>45999</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>45999</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15189,7 +15189,7 @@
         <v>46001</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15262,7 +15262,7 @@
         <v>46003</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
         <v>46003</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>45783</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>46230</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15559,7 +15559,7 @@
         <v>46006</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15632,7 +15632,7 @@
         <v>46009</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15705,7 +15705,7 @@
         <v>46009</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15778,7 +15778,7 @@
         <v>46282</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15851,7 +15851,7 @@
         <v>45636</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15924,7 +15924,7 @@
         <v>46281</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>46281</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16075,7 +16075,7 @@
         <v>45792</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16153,7 +16153,7 @@
         <v>46282</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>46282</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>45792</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
         <v>45792</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>44805</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>46034</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>45792</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>46034</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16752,7 +16752,7 @@
         <v>46286</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>46036</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>45268</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>46038</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17049,7 +17049,7 @@
         <v>46038</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17122,7 +17122,7 @@
         <v>46038</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>45686</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>45282</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>45407</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>45700</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>45553</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
         <v>45575</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>45798</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>46048</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>45799</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>46049</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>45802</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>46051</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>45805</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18159,7 +18159,7 @@
         <v>45805</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>45810</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>45810</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>45812</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>46293</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>44941</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>45812</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>45820</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>45243</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>45246</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18904,7 +18904,7 @@
         <v>45364</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>45364</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>45378</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>45385</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19196,7 +19196,7 @@
         <v>45364</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>45827</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>46083</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>46213</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>45833</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19566,7 +19566,7 @@
         <v>45833</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>45832</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>45513</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>45833</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>45664</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>46092</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>46287</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20082,7 +20082,7 @@
         <v>46092</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>46092</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>46094</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>46094</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>46094</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>46101</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
         <v>46101</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20628,7 +20628,7 @@
         <v>46302</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>46106</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>46107</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20852,7 +20852,7 @@
         <v>45782</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20925,7 +20925,7 @@
         <v>44965</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>44656</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>45876</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
         <v>45112</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21227,7 +21227,7 @@
         <v>45876</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21305,7 +21305,7 @@
         <v>46129</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21383,7 +21383,7 @@
         <v>45112</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>44917</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         <v>46132</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>44918</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>44497</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
         <v>45593</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>45366</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21904,7 +21904,7 @@
         <v>45121</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21977,7 +21977,7 @@
         <v>45644</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22050,7 +22050,7 @@
         <v>44917</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22123,7 +22123,7 @@
         <v>45887</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>45904</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22269,7 +22269,7 @@
         <v>45888</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22342,7 +22342,7 @@
         <v>45359</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22415,7 +22415,7 @@
         <v>45811</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
         <v>46307</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22561,7 +22561,7 @@
         <v>45888</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22634,7 +22634,7 @@
         <v>46140</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22712,7 +22712,7 @@
         <v>46139</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>45933</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44677</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22931,7 +22931,7 @@
         <v>44974</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23004,7 +23004,7 @@
         <v>45804</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>46136</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23150,7 +23150,7 @@
         <v>46140</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23228,7 +23228,7 @@
         <v>45756</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>45370</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23379,7 +23379,7 @@
         <v>45379</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23452,7 +23452,7 @@
         <v>45999</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23530,7 +23530,7 @@
         <v>45127</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23603,7 +23603,7 @@
         <v>46141</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>46141</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23759,7 +23759,7 @@
         <v>45625</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>46274</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>46274</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>44722</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>45827</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>46141</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24202,7 +24202,7 @@
         <v>44637</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24275,7 +24275,7 @@
         <v>45453</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>46150</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24426,7 +24426,7 @@
         <v>46149</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>46150</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24577,7 +24577,7 @@
         <v>46154</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24650,7 +24650,7 @@
         <v>45022</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24723,7 +24723,7 @@
         <v>45341</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>45341</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>45569</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>45239</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25015,7 +25015,7 @@
         <v>44722</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>44722</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
         <v>45041</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25234,7 +25234,7 @@
         <v>45267</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25307,7 +25307,7 @@
         <v>44753</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25380,7 +25380,7 @@
         <v>45361</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>45600</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25526,7 +25526,7 @@
         <v>45118</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>45058</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>44712</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25750,7 +25750,7 @@
         <v>45662</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>44924</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>45119</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25969,7 +25969,7 @@
         <v>45141</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26042,7 +26042,7 @@
         <v>45749</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26115,7 +26115,7 @@
         <v>45202</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26188,7 +26188,7 @@
         <v>45701</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>45666</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26339,7 +26339,7 @@
         <v>45656</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26412,7 +26412,7 @@
         <v>45442</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26485,7 +26485,7 @@
         <v>44987</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>45647</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>45002</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26704,7 +26704,7 @@
         <v>45176</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26782,7 +26782,7 @@
         <v>45686</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>44894</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>44533</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>44917</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>45260</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>45253</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>44847</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>45226</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27366,7 +27366,7 @@
         <v>45226</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>45076</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>44525</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         <v>45366</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27658,7 +27658,7 @@
         <v>44923</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27731,7 +27731,7 @@
         <v>45272</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>45167</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>45081</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>45313</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>45679</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>44994</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28174,7 +28174,7 @@
         <v>45110</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28247,7 +28247,7 @@
         <v>45081</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>45252</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28393,7 +28393,7 @@
         <v>45238</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28471,7 +28471,7 @@
         <v>45379</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28544,7 +28544,7 @@
         <v>45379</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28617,7 +28617,7 @@
         <v>44985</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28690,7 +28690,7 @@
         <v>45387</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>45324</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>44959</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
         <v>44851</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>45392</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29065,7 +29065,7 @@
         <v>45000</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>45110</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29211,7 +29211,7 @@
         <v>45461</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29284,7 +29284,7 @@
         <v>45456</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29357,7 +29357,7 @@
         <v>45079</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29430,7 +29430,7 @@
         <v>45188</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29503,7 +29503,7 @@
         <v>45442</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         <v>45595</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29649,7 +29649,7 @@
         <v>45622</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29722,7 +29722,7 @@
         <v>44588</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>44588</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>45600</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>45082</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30019,7 +30019,7 @@
         <v>45268</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30092,7 +30092,7 @@
         <v>45478</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30165,7 +30165,7 @@
         <v>45450</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
         <v>44648</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30316,7 +30316,7 @@
         <v>45198</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30389,7 +30389,7 @@
         <v>45044</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30462,7 +30462,7 @@
         <v>45313</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         <v>45456</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>44812</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30681,7 +30681,7 @@
         <v>44734</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30754,7 +30754,7 @@
         <v>44722</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30827,7 +30827,7 @@
         <v>44722</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30900,7 +30900,7 @@
         <v>45666</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30973,7 +30973,7 @@
         <v>45181</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31051,7 +31051,7 @@
         <v>45202</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>45769</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31202,7 +31202,7 @@
         <v>45243</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31275,7 +31275,7 @@
         <v>44749</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31348,7 +31348,7 @@
         <v>45701</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31426,7 +31426,7 @@
         <v>45631</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31499,7 +31499,7 @@
         <v>45191</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31572,7 +31572,7 @@
         <v>45201</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31645,7 +31645,7 @@
         <v>45302</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31718,7 +31718,7 @@
         <v>45159</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31796,7 +31796,7 @@
         <v>45315</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31869,7 +31869,7 @@
         <v>45770</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31942,7 +31942,7 @@
         <v>45344</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32020,7 +32020,7 @@
         <v>44831</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>45097</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32166,7 +32166,7 @@
         <v>45202</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32239,7 +32239,7 @@
         <v>45303</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>45379</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32385,7 +32385,7 @@
         <v>45244</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32458,7 +32458,7 @@
         <v>45681</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32536,7 +32536,7 @@
         <v>45678</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32609,7 +32609,7 @@
         <v>45386</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>45302</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32755,7 +32755,7 @@
         <v>45681</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32833,7 +32833,7 @@
         <v>45477</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>45268</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32979,7 +32979,7 @@
         <v>44651</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33052,7 +33052,7 @@
         <v>44841</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33125,7 +33125,7 @@
         <v>44741</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33201,7 +33201,7 @@
         <v>43980</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33274,7 +33274,7 @@
         <v>44657</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33347,7 +33347,7 @@
         <v>44711</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33420,7 +33420,7 @@
         <v>44690</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33493,7 +33493,7 @@
         <v>45247</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>45247</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33649,7 +33649,7 @@
         <v>45103</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>45442</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33795,7 +33795,7 @@
         <v>45463</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33873,7 +33873,7 @@
         <v>45475</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33946,7 +33946,7 @@
         <v>45533</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34019,7 +34019,7 @@
         <v>45442</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34092,7 +34092,7 @@
         <v>44985</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34165,7 +34165,7 @@
         <v>45414</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34238,7 +34238,7 @@
         <v>45442</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34311,7 +34311,7 @@
         <v>45533</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34384,7 +34384,7 @@
         <v>45118</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>45247</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34535,7 +34535,7 @@
         <v>45512</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34608,7 +34608,7 @@
         <v>45783</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34686,7 +34686,7 @@
         <v>45792</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34764,7 +34764,7 @@
         <v>45805</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34842,7 +34842,7 @@
         <v>46040</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34915,7 +34915,7 @@
         <v>46106</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34993,7 +34993,7 @@
         <v>46036</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>

--- a/Översikt KRISTINEHAMN.xlsx
+++ b/Översikt KRISTINEHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45229</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>45229</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45727</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>45118</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>45265</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>45091</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45561</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>45562</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>45113</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>44690</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45233</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>44525</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>44769</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>44574</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>44525</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>44614</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>45154</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>45960</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>45960</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>45982</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>45693</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>46000</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>45674</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>45804</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         <v>45996</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>45819</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>46101</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>46101</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>44584</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>46141</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>45637</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>44843</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>44883</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>45002</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>45380</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>45356</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>44337</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>44693</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>45579</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>45247</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>45716</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>45812</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>44831</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         <v>44659</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>44683</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>44634</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>44734</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>44559</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>44851</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>44497</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>44536</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>44741</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>44576</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>44791</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>44588</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6095,7 +6095,7 @@
         <v>44588</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>44769</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>44829</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>44834</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>44657</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>44518</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>44497</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>44551</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>44501</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>44657</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>44707</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>44662</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         <v>44742</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
         <v>44810</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>44880</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         <v>44853</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7263,7 +7263,7 @@
         <v>44573</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>44855</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         <v>44706</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         <v>44591</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>44518</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>44518</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>44501</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>44741</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>44584</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>44825</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         <v>44707</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         <v>44706</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>45625</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         <v>45302</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>45477</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>44742</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>45208</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         <v>45377</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>45202</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>45202</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>44770</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>45203</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>45460</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>45902</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>45904</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>45905</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>46161</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>46162</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>45222</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>45478</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>45478</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>45098</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>45098</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>45701</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>44526</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>44526</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>45104</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         <v>44595</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>44595</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         <v>45803</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10223,7 +10223,7 @@
         <v>46170</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>46171</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>45243</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         <v>45243</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         <v>45243</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
         <v>45933</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         <v>45322</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>45266</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>44978</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>44746</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
         <v>45639</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>45265</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         <v>45450</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>46175</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>45095</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>45944</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>45072</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11484,7 +11484,7 @@
         <v>45429</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>45282</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11630,7 +11630,7 @@
         <v>45447</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>45167</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>44855</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>45393</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>44888</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>44972</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>45952</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>46037</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>45068</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12287,7 +12287,7 @@
         <v>45202</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>45401</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12433,7 +12433,7 @@
         <v>45954</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>45141</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>45243</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>45243</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>45959</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>45961</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>45961</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>46190</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>45315</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>46190</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>45243</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>45167</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         <v>45323</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>45974</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>44985</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>44991</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13621,7 +13621,7 @@
         <v>45631</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>44742</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>45705</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>45734</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         <v>45202</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>46205</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>46205</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>45222</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>45379</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>45636</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>44883</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         <v>45679</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>45995</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>45995</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>46000</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>45999</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14804,7 +14804,7 @@
         <v>46000</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>45685</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         <v>45999</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>45999</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>45999</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15189,7 +15189,7 @@
         <v>46001</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15262,7 +15262,7 @@
         <v>46003</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
         <v>46003</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>45783</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>46230</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15559,7 +15559,7 @@
         <v>46006</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15632,7 +15632,7 @@
         <v>46009</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15705,7 +15705,7 @@
         <v>46009</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15778,7 +15778,7 @@
         <v>46282</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15851,7 +15851,7 @@
         <v>45636</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15924,7 +15924,7 @@
         <v>46281</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>46281</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16075,7 +16075,7 @@
         <v>45792</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16153,7 +16153,7 @@
         <v>46282</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>46282</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>45792</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
         <v>45792</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>44805</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>46034</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>45792</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>46034</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16752,7 +16752,7 @@
         <v>46286</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>46036</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>45268</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>46038</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17049,7 +17049,7 @@
         <v>46038</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17122,7 +17122,7 @@
         <v>46038</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>45686</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>45282</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>45407</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>45700</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>45553</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
         <v>45575</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>45798</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>46048</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>45799</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>46049</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>45802</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>46051</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>45805</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18159,7 +18159,7 @@
         <v>45805</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>45810</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>45810</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>45812</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>46293</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>44941</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>45812</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>45820</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>45243</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>45246</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18904,7 +18904,7 @@
         <v>45364</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>45364</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>45378</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>45385</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19196,7 +19196,7 @@
         <v>45364</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>45827</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>46083</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>46213</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>45833</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19566,7 +19566,7 @@
         <v>45833</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>45832</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>45513</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>45833</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>45664</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>46092</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>46287</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20082,7 +20082,7 @@
         <v>46092</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>46092</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>46094</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>46094</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>46094</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>46101</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
         <v>46101</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20628,7 +20628,7 @@
         <v>46302</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>46106</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>46107</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20852,7 +20852,7 @@
         <v>45782</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20925,7 +20925,7 @@
         <v>44965</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>44656</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>45876</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
         <v>45112</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21227,7 +21227,7 @@
         <v>45876</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21305,7 +21305,7 @@
         <v>46129</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21383,7 +21383,7 @@
         <v>45112</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>44917</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         <v>46132</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>44918</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>44497</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
         <v>45593</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>45366</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21904,7 +21904,7 @@
         <v>45121</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21977,7 +21977,7 @@
         <v>45644</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22050,7 +22050,7 @@
         <v>44917</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22123,7 +22123,7 @@
         <v>45887</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>45904</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22269,7 +22269,7 @@
         <v>45888</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22342,7 +22342,7 @@
         <v>45359</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22415,7 +22415,7 @@
         <v>45811</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
         <v>46307</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22561,7 +22561,7 @@
         <v>45888</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22634,7 +22634,7 @@
         <v>46140</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22712,7 +22712,7 @@
         <v>46139</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>45933</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44677</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22931,7 +22931,7 @@
         <v>44974</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23004,7 +23004,7 @@
         <v>45804</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>46136</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23150,7 +23150,7 @@
         <v>46140</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23228,7 +23228,7 @@
         <v>45756</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>45370</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23379,7 +23379,7 @@
         <v>45379</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23452,7 +23452,7 @@
         <v>45999</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23530,7 +23530,7 @@
         <v>45127</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23603,7 +23603,7 @@
         <v>46141</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>46141</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23759,7 +23759,7 @@
         <v>45625</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>46274</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>46274</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>44722</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>45827</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>46141</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24202,7 +24202,7 @@
         <v>44637</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24275,7 +24275,7 @@
         <v>45453</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>46150</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24426,7 +24426,7 @@
         <v>46149</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>46150</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24577,7 +24577,7 @@
         <v>46154</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24650,7 +24650,7 @@
         <v>45022</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24723,7 +24723,7 @@
         <v>45341</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>45341</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>45569</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>45239</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25015,7 +25015,7 @@
         <v>44722</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>44722</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
         <v>45041</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25234,7 +25234,7 @@
         <v>45267</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25307,7 +25307,7 @@
         <v>44753</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25380,7 +25380,7 @@
         <v>45361</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>45600</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25526,7 +25526,7 @@
         <v>45118</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>45058</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>44712</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25750,7 +25750,7 @@
         <v>45662</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>44924</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>45119</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25969,7 +25969,7 @@
         <v>45141</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26042,7 +26042,7 @@
         <v>45749</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26115,7 +26115,7 @@
         <v>45202</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26188,7 +26188,7 @@
         <v>45701</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>45666</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26339,7 +26339,7 @@
         <v>45656</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26412,7 +26412,7 @@
         <v>45442</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26485,7 +26485,7 @@
         <v>44987</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>45647</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>45002</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26704,7 +26704,7 @@
         <v>45176</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26782,7 +26782,7 @@
         <v>45686</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>44894</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>44533</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>44917</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>45260</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>45253</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>44847</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>45226</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27366,7 +27366,7 @@
         <v>45226</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>45076</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>44525</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         <v>45366</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27658,7 +27658,7 @@
         <v>44923</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27731,7 +27731,7 @@
         <v>45272</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>45167</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>45081</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>45313</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>45679</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>44994</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28174,7 +28174,7 @@
         <v>45110</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28247,7 +28247,7 @@
         <v>45081</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>45252</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28393,7 +28393,7 @@
         <v>45238</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28471,7 +28471,7 @@
         <v>45379</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28544,7 +28544,7 @@
         <v>45379</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28617,7 +28617,7 @@
         <v>44985</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28690,7 +28690,7 @@
         <v>45387</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>45324</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>44959</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
         <v>44851</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>45392</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29065,7 +29065,7 @@
         <v>45000</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>45110</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29211,7 +29211,7 @@
         <v>45461</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29284,7 +29284,7 @@
         <v>45456</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29357,7 +29357,7 @@
         <v>45079</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29430,7 +29430,7 @@
         <v>45188</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29503,7 +29503,7 @@
         <v>45442</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         <v>45595</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29649,7 +29649,7 @@
         <v>45622</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29722,7 +29722,7 @@
         <v>44588</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>44588</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>45600</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>45082</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30019,7 +30019,7 @@
         <v>45268</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30092,7 +30092,7 @@
         <v>45478</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30165,7 +30165,7 @@
         <v>45450</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
         <v>44648</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30316,7 +30316,7 @@
         <v>45198</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30389,7 +30389,7 @@
         <v>45044</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30462,7 +30462,7 @@
         <v>45313</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         <v>45456</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>44812</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30681,7 +30681,7 @@
         <v>44734</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30754,7 +30754,7 @@
         <v>44722</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30827,7 +30827,7 @@
         <v>44722</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30900,7 +30900,7 @@
         <v>45666</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30973,7 +30973,7 @@
         <v>45181</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31051,7 +31051,7 @@
         <v>45202</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>45769</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31202,7 +31202,7 @@
         <v>45243</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31275,7 +31275,7 @@
         <v>44749</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31348,7 +31348,7 @@
         <v>45701</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31426,7 +31426,7 @@
         <v>45631</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31499,7 +31499,7 @@
         <v>45191</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31572,7 +31572,7 @@
         <v>45201</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31645,7 +31645,7 @@
         <v>45302</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31718,7 +31718,7 @@
         <v>45159</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31796,7 +31796,7 @@
         <v>45315</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31869,7 +31869,7 @@
         <v>45770</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31942,7 +31942,7 @@
         <v>45344</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32020,7 +32020,7 @@
         <v>44831</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>45097</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32166,7 +32166,7 @@
         <v>45202</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32239,7 +32239,7 @@
         <v>45303</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>45379</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32385,7 +32385,7 @@
         <v>45244</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32458,7 +32458,7 @@
         <v>45681</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32536,7 +32536,7 @@
         <v>45678</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32609,7 +32609,7 @@
         <v>45386</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>45302</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32755,7 +32755,7 @@
         <v>45681</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32833,7 +32833,7 @@
         <v>45477</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>45268</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32979,7 +32979,7 @@
         <v>44651</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33052,7 +33052,7 @@
         <v>44841</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33125,7 +33125,7 @@
         <v>44741</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33201,7 +33201,7 @@
         <v>43980</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33274,7 +33274,7 @@
         <v>44657</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33347,7 +33347,7 @@
         <v>44711</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33420,7 +33420,7 @@
         <v>44690</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33493,7 +33493,7 @@
         <v>45247</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>45247</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33649,7 +33649,7 @@
         <v>45103</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>45442</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33795,7 +33795,7 @@
         <v>45463</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33873,7 +33873,7 @@
         <v>45475</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33946,7 +33946,7 @@
         <v>45533</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34019,7 +34019,7 @@
         <v>45442</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34092,7 +34092,7 @@
         <v>44985</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34165,7 +34165,7 @@
         <v>45414</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34238,7 +34238,7 @@
         <v>45442</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34311,7 +34311,7 @@
         <v>45533</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34384,7 +34384,7 @@
         <v>45118</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>45247</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34535,7 +34535,7 @@
         <v>45512</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34608,7 +34608,7 @@
         <v>45783</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34686,7 +34686,7 @@
         <v>45792</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34764,7 +34764,7 @@
         <v>45805</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34842,7 +34842,7 @@
         <v>46040</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34915,7 +34915,7 @@
         <v>46106</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34993,7 +34993,7 @@
         <v>46036</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
